--- a/database/event/8044/event_8044_evp_summary.xlsx
+++ b/database/event/8044/event_8044_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.8548</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.5246</v>
       </c>
       <c r="D2" t="n">
         <v>2.7518</v>
@@ -545,7 +545,7 @@
         <v>7.6686</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.4648</v>
       </c>
       <c r="D3" t="n">
         <v>2.6766</v>
@@ -591,7 +591,7 @@
         <v>7.1656</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.3031</v>
       </c>
       <c r="D4" t="n">
         <v>2.4734</v>
@@ -637,7 +637,7 @@
         <v>6.5584</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.1079</v>
       </c>
       <c r="D5" t="n">
         <v>2.2281</v>
@@ -683,7 +683,7 @@
         <v>6.3322</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.0352</v>
       </c>
       <c r="D6" t="n">
         <v>2.1367</v>
@@ -729,7 +729,7 @@
         <v>5.8621</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.8841</v>
       </c>
       <c r="D7" t="n">
         <v>1.9468</v>
@@ -775,7 +775,7 @@
         <v>5.5308</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.7777</v>
       </c>
       <c r="D8" t="n">
         <v>1.813</v>
@@ -821,7 +821,7 @@
         <v>5.4066</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="D9" t="n">
         <v>1.7628</v>
@@ -867,7 +867,7 @@
         <v>4.2807</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.3759</v>
       </c>
       <c r="D10" t="n">
         <v>1.3079</v>
@@ -913,7 +913,7 @@
         <v>4.22</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.3564</v>
       </c>
       <c r="D11" t="n">
         <v>1.2834</v>
@@ -959,7 +959,7 @@
         <v>4.1188</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.3238</v>
       </c>
       <c r="D12" t="n">
         <v>1.2425</v>
@@ -1005,7 +1005,7 @@
         <v>4.1097</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="D13" t="n">
         <v>1.2389</v>
@@ -1051,7 +1051,7 @@
         <v>3.9369</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.2654</v>
       </c>
       <c r="D14" t="n">
         <v>1.1691</v>
@@ -1097,7 +1097,7 @@
         <v>3.7655</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.2103</v>
       </c>
       <c r="D15" t="n">
         <v>1.0998</v>
@@ -1143,7 +1143,7 @@
         <v>3.6973</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.1884</v>
       </c>
       <c r="D16" t="n">
         <v>1.0723</v>
@@ -1189,7 +1189,7 @@
         <v>3.6428</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.1708</v>
       </c>
       <c r="D17" t="n">
         <v>1.0502</v>
@@ -1235,7 +1235,7 @@
         <v>3.6274</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.1659</v>
       </c>
       <c r="D18" t="n">
         <v>1.044</v>
@@ -1281,7 +1281,7 @@
         <v>3.5956</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.1557</v>
       </c>
       <c r="D19" t="n">
         <v>1.0312</v>
@@ -1327,7 +1327,7 @@
         <v>3.5589</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.1439</v>
       </c>
       <c r="D20" t="n">
         <v>1.0164</v>
@@ -1373,7 +1373,7 @@
         <v>3.4062</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.0948</v>
       </c>
       <c r="D21" t="n">
         <v>0.9547</v>
@@ -1419,7 +1419,7 @@
         <v>3.3139</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.0651</v>
       </c>
       <c r="D22" t="n">
         <v>0.9174</v>
@@ -1465,7 +1465,7 @@
         <v>3.2937</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0586</v>
       </c>
       <c r="D23" t="n">
         <v>0.9092</v>
@@ -1511,7 +1511,7 @@
         <v>3.2604</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0479</v>
       </c>
       <c r="D24" t="n">
         <v>0.8958</v>
@@ -1557,7 +1557,7 @@
         <v>3.2428</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0423</v>
       </c>
       <c r="D25" t="n">
         <v>0.8887</v>
@@ -1603,7 +1603,7 @@
         <v>3.095</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9948</v>
       </c>
       <c r="D26" t="n">
         <v>0.8289</v>
@@ -1649,7 +1649,7 @@
         <v>2.8614</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9197</v>
       </c>
       <c r="D27" t="n">
         <v>0.7346</v>
@@ -1695,7 +1695,7 @@
         <v>2.7517</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8844</v>
       </c>
       <c r="D28" t="n">
         <v>0.6903</v>
@@ -1741,7 +1741,7 @@
         <v>2.6343</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8467</v>
       </c>
       <c r="D29" t="n">
         <v>0.6428</v>
@@ -1787,7 +1787,7 @@
         <v>2.5596</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8227</v>
       </c>
       <c r="D30" t="n">
         <v>0.6127</v>
@@ -1833,7 +1833,7 @@
         <v>2.3324</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7497</v>
       </c>
       <c r="D31" t="n">
         <v>0.5209</v>
@@ -1879,7 +1879,7 @@
         <v>2.1341</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6859</v>
       </c>
       <c r="D32" t="n">
         <v>0.4408</v>
@@ -1925,7 +1925,7 @@
         <v>2.1256</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6832</v>
       </c>
       <c r="D33" t="n">
         <v>0.4373</v>
@@ -1971,7 +1971,7 @@
         <v>2.1141</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6795</v>
       </c>
       <c r="D34" t="n">
         <v>0.4327</v>
@@ -2017,7 +2017,7 @@
         <v>2.0853</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6702</v>
       </c>
       <c r="D35" t="n">
         <v>0.4211</v>
@@ -2063,7 +2063,7 @@
         <v>2.0633</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6632</v>
       </c>
       <c r="D36" t="n">
         <v>0.4122</v>
@@ -2109,7 +2109,7 @@
         <v>2.0144</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6475</v>
       </c>
       <c r="D37" t="n">
         <v>0.3924</v>
@@ -2155,7 +2155,7 @@
         <v>1.8314</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5886</v>
       </c>
       <c r="D38" t="n">
         <v>0.3185</v>
@@ -2201,7 +2201,7 @@
         <v>1.5061</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4841</v>
       </c>
       <c r="D39" t="n">
         <v>0.1871</v>
@@ -2247,7 +2247,7 @@
         <v>1.3033</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4189</v>
       </c>
       <c r="D40" t="n">
         <v>0.1051</v>
@@ -2293,7 +2293,7 @@
         <v>1.1622</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3735</v>
       </c>
       <c r="D41" t="n">
         <v>0.0481</v>
@@ -2339,7 +2339,7 @@
         <v>1.1327</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3641</v>
       </c>
       <c r="D42" t="n">
         <v>0.0362</v>
@@ -2385,7 +2385,7 @@
         <v>1.0921</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="D43" t="n">
         <v>0.0198</v>
@@ -2431,7 +2431,7 @@
         <v>0.9869</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3172</v>
       </c>
       <c r="D44" t="n">
         <v>-0.0227</v>
@@ -2477,7 +2477,7 @@
         <v>0.9181</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2951</v>
       </c>
       <c r="D45" t="n">
         <v>-0.0505</v>
@@ -2523,7 +2523,7 @@
         <v>0.8411999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2704</v>
       </c>
       <c r="D46" t="n">
         <v>-0.0815</v>
@@ -2569,7 +2569,7 @@
         <v>0.8391</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2697</v>
       </c>
       <c r="D47" t="n">
         <v>-0.0824</v>
@@ -2615,7 +2615,7 @@
         <v>0.7308</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2349</v>
       </c>
       <c r="D48" t="n">
         <v>-0.1261</v>
@@ -2661,7 +2661,7 @@
         <v>0.6958</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2236</v>
       </c>
       <c r="D49" t="n">
         <v>-0.1403</v>
@@ -2707,7 +2707,7 @@
         <v>0.5929</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1906</v>
       </c>
       <c r="D50" t="n">
         <v>-0.1818</v>
@@ -2753,7 +2753,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1813</v>
       </c>
       <c r="D51" t="n">
         <v>-0.1935</v>
@@ -2799,7 +2799,7 @@
         <v>0.4998</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1606</v>
       </c>
       <c r="D52" t="n">
         <v>-0.2195</v>
@@ -2845,7 +2845,7 @@
         <v>0.4124</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.1325</v>
       </c>
       <c r="D53" t="n">
         <v>-0.2548</v>
@@ -2891,7 +2891,7 @@
         <v>0.3368</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
       <c r="D54" t="n">
         <v>-0.2853</v>
@@ -2937,7 +2937,7 @@
         <v>0.2978</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3011</v>
@@ -2983,7 +2983,7 @@
         <v>0.1881</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="D56" t="n">
         <v>-0.3454</v>
@@ -3029,7 +3029,7 @@
         <v>0.1832</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.0589</v>
       </c>
       <c r="D57" t="n">
         <v>-0.3474</v>
@@ -3075,7 +3075,7 @@
         <v>0.1567</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>0.0504</v>
       </c>
       <c r="D58" t="n">
         <v>-0.3581</v>
@@ -3121,7 +3121,7 @@
         <v>0.1417</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.0455</v>
       </c>
       <c r="D59" t="n">
         <v>-0.3641</v>
@@ -3167,7 +3167,7 @@
         <v>0.0529</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D60" t="n">
         <v>-0.4</v>
@@ -3213,7 +3213,7 @@
         <v>-0.1624</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.0522</v>
       </c>
       <c r="D61" t="n">
         <v>-0.487</v>
@@ -3259,7 +3259,7 @@
         <v>-0.2397</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.077</v>
       </c>
       <c r="D62" t="n">
         <v>-0.5182</v>
@@ -3305,7 +3305,7 @@
         <v>-0.2487</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.0799</v>
       </c>
       <c r="D63" t="n">
         <v>-0.5218</v>
@@ -3351,7 +3351,7 @@
         <v>-0.3161</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.1016</v>
       </c>
       <c r="D64" t="n">
         <v>-0.5491</v>
@@ -3397,7 +3397,7 @@
         <v>-1.0923</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3511</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8626</v>
@@ -3443,7 +3443,7 @@
         <v>-1.1918</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3831</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9028</v>
@@ -3489,7 +3489,7 @@
         <v>-1.2046</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.3872</v>
       </c>
       <c r="D67" t="n">
         <v>-0.908</v>
@@ -3535,7 +3535,7 @@
         <v>-1.3248</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.4258</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9566</v>
@@ -3581,7 +3581,7 @@
         <v>-1.477</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4747</v>
       </c>
       <c r="D69" t="n">
         <v>-1.018</v>
@@ -3627,7 +3627,7 @@
         <v>-1.5713</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.505</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0561</v>
@@ -3673,7 +3673,7 @@
         <v>-1.7682</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.5683</v>
       </c>
       <c r="D71" t="n">
         <v>-1.1357</v>
@@ -3719,7 +3719,7 @@
         <v>-1.9474</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.6259</v>
       </c>
       <c r="D72" t="n">
         <v>-1.2081</v>
@@ -3765,7 +3765,7 @@
         <v>-2.0625</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.6629</v>
       </c>
       <c r="D73" t="n">
         <v>-1.2546</v>
@@ -3811,7 +3811,7 @@
         <v>-2.2826</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.7337</v>
       </c>
       <c r="D74" t="n">
         <v>-1.3435</v>
@@ -3857,7 +3857,7 @@
         <v>-2.4133</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="D75" t="n">
         <v>-1.3963</v>
@@ -3903,7 +3903,7 @@
         <v>-2.8238</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.9076</v>
       </c>
       <c r="D76" t="n">
         <v>-1.5621</v>
@@ -3949,7 +3949,7 @@
         <v>-2.8766</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.9246</v>
       </c>
       <c r="D77" t="n">
         <v>-1.5834</v>
@@ -3995,7 +3995,7 @@
         <v>-2.9843</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="D78" t="n">
         <v>-1.627</v>
@@ -4041,7 +4041,7 @@
         <v>-3.7364</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.2009</v>
       </c>
       <c r="D79" t="n">
         <v>-1.9308</v>
@@ -4087,7 +4087,7 @@
         <v>-3.9875</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.2816</v>
       </c>
       <c r="D80" t="n">
         <v>-2.0322</v>
@@ -4133,7 +4133,7 @@
         <v>-4.0518</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.3023</v>
       </c>
       <c r="D81" t="n">
         <v>-2.0582</v>

--- a/database/event/8044/event_8044_evp_summary.xlsx
+++ b/database/event/8044/event_8044_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8548</v>
+        <v>7.8409</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5246</v>
+        <v>2.5202</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7518</v>
+        <v>2.6799</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8548</v>
+        <v>7.8409</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7348</v>
+        <v>3.7209</v>
       </c>
       <c r="G2" t="n">
         <v>4.12</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7348</v>
+        <v>3.7209</v>
       </c>
       <c r="I2" t="n">
         <v>3.7522</v>
@@ -548,7 +548,7 @@
         <v>2.4648</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6766</v>
+        <v>2.6113</v>
       </c>
       <c r="E3" t="n">
         <v>7.6686</v>
@@ -594,7 +594,7 @@
         <v>2.3031</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4734</v>
+        <v>2.4109</v>
       </c>
       <c r="E4" t="n">
         <v>7.1656</v>
@@ -640,7 +640,7 @@
         <v>2.1079</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2281</v>
+        <v>2.169</v>
       </c>
       <c r="E5" t="n">
         <v>6.5584</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.3322</v>
+        <v>6.3192</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0352</v>
+        <v>2.0311</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1367</v>
+        <v>2.0737</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3322</v>
+        <v>6.3192</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9612</v>
+        <v>4.9482</v>
       </c>
       <c r="G6" t="n">
         <v>1.371</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4761</v>
+        <v>5.4557</v>
       </c>
       <c r="I6" t="n">
         <v>5.5016</v>
@@ -732,7 +732,7 @@
         <v>1.8841</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9468</v>
+        <v>1.8916</v>
       </c>
       <c r="E7" t="n">
         <v>5.8621</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5308</v>
+        <v>5.517</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7777</v>
+        <v>1.7732</v>
       </c>
       <c r="D8" t="n">
-        <v>1.813</v>
+        <v>1.7541</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5308</v>
+        <v>5.517</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1725</v>
+        <v>5.1587</v>
       </c>
       <c r="G8" t="n">
         <v>0.3583</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8074</v>
+        <v>5.7857</v>
       </c>
       <c r="I8" t="n">
         <v>5.8344</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.4066</v>
+        <v>5.3921</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7377</v>
+        <v>1.7331</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7628</v>
+        <v>1.7043</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4066</v>
+        <v>5.3921</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8889</v>
+        <v>3.8744</v>
       </c>
       <c r="G9" t="n">
         <v>1.5178</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8889</v>
+        <v>3.8744</v>
       </c>
       <c r="I9" t="n">
         <v>3.907</v>
@@ -870,7 +870,7 @@
         <v>1.3759</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3079</v>
+        <v>1.2615</v>
       </c>
       <c r="E10" t="n">
         <v>4.2807</v>
@@ -916,7 +916,7 @@
         <v>1.3564</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2834</v>
+        <v>1.2373</v>
       </c>
       <c r="E11" t="n">
         <v>4.22</v>
@@ -962,7 +962,7 @@
         <v>1.3238</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2425</v>
+        <v>1.197</v>
       </c>
       <c r="E12" t="n">
         <v>4.1188</v>
@@ -1008,7 +1008,7 @@
         <v>1.3209</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2389</v>
+        <v>1.1934</v>
       </c>
       <c r="E13" t="n">
         <v>4.1097</v>
@@ -1054,7 +1054,7 @@
         <v>1.2654</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1691</v>
+        <v>1.1246</v>
       </c>
       <c r="E14" t="n">
         <v>3.9369</v>
@@ -1100,7 +1100,7 @@
         <v>1.2103</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0998</v>
+        <v>1.0563</v>
       </c>
       <c r="E15" t="n">
         <v>3.7655</v>
@@ -1146,7 +1146,7 @@
         <v>1.1884</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0723</v>
+        <v>1.0291</v>
       </c>
       <c r="E16" t="n">
         <v>3.6973</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.6428</v>
+        <v>3.6323</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1708</v>
+        <v>1.1675</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0502</v>
+        <v>1.0032</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6428</v>
+        <v>3.6323</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2828</v>
+        <v>4.2723</v>
       </c>
       <c r="G17" t="n">
         <v>-0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4124</v>
+        <v>4.3959</v>
       </c>
       <c r="I17" t="n">
         <v>4.4329</v>
@@ -1238,7 +1238,7 @@
         <v>1.1659</v>
       </c>
       <c r="D18" t="n">
-        <v>1.044</v>
+        <v>1.0012</v>
       </c>
       <c r="E18" t="n">
         <v>3.6274</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5956</v>
+        <v>3.5913</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1557</v>
+        <v>1.1543</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0312</v>
+        <v>0.9869</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5956</v>
+        <v>3.5913</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1471</v>
+        <v>1.1428</v>
       </c>
       <c r="G19" t="n">
         <v>2.4485</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1471</v>
+        <v>1.1428</v>
       </c>
       <c r="I19" t="n">
         <v>1.1524</v>
@@ -1330,7 +1330,7 @@
         <v>1.1439</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0164</v>
+        <v>0.974</v>
       </c>
       <c r="E20" t="n">
         <v>3.5589</v>
@@ -1376,7 +1376,7 @@
         <v>1.0948</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9547</v>
+        <v>0.9131</v>
       </c>
       <c r="E21" t="n">
         <v>3.4062</v>
@@ -1422,7 +1422,7 @@
         <v>1.0651</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9174</v>
+        <v>0.8763</v>
       </c>
       <c r="E22" t="n">
         <v>3.3139</v>
@@ -1468,7 +1468,7 @@
         <v>1.0586</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9092</v>
+        <v>0.8683</v>
       </c>
       <c r="E23" t="n">
         <v>3.2937</v>
@@ -1514,7 +1514,7 @@
         <v>1.0479</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8958</v>
+        <v>0.855</v>
       </c>
       <c r="E24" t="n">
         <v>3.2604</v>
@@ -1560,7 +1560,7 @@
         <v>1.0423</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8887</v>
+        <v>0.848</v>
       </c>
       <c r="E25" t="n">
         <v>3.2428</v>
@@ -1606,7 +1606,7 @@
         <v>0.9948</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8289</v>
+        <v>0.7891</v>
       </c>
       <c r="E26" t="n">
         <v>3.095</v>
@@ -1652,7 +1652,7 @@
         <v>0.9197</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7346</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>2.8614</v>
@@ -1698,7 +1698,7 @@
         <v>0.8844</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6903</v>
+        <v>0.6524</v>
       </c>
       <c r="E28" t="n">
         <v>2.7517</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.6343</v>
+        <v>2.6298</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8467</v>
+        <v>0.8452</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6428</v>
+        <v>0.6038</v>
       </c>
       <c r="E29" t="n">
-        <v>2.6343</v>
+        <v>2.6298</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1918</v>
+        <v>1.1874</v>
       </c>
       <c r="G29" t="n">
         <v>1.4425</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1918</v>
+        <v>1.1874</v>
       </c>
       <c r="I29" t="n">
         <v>1.1974</v>
@@ -1790,7 +1790,7 @@
         <v>0.8227</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6127</v>
+        <v>0.5758</v>
       </c>
       <c r="E30" t="n">
         <v>2.5596</v>
@@ -1836,7 +1836,7 @@
         <v>0.7497</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5209</v>
+        <v>0.4853</v>
       </c>
       <c r="E31" t="n">
         <v>2.3324</v>
@@ -1882,7 +1882,7 @@
         <v>0.6859</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4408</v>
+        <v>0.4063</v>
       </c>
       <c r="E32" t="n">
         <v>2.1341</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1256</v>
+        <v>2.1141</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6832</v>
+        <v>0.6795</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4373</v>
+        <v>0.3983</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1256</v>
+        <v>2.1141</v>
       </c>
       <c r="F33" t="n">
-        <v>3.2189</v>
+        <v>3.1141</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.0933</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2189</v>
+        <v>3.1141</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2339</v>
+        <v>3.1141</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0933</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="L33" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1406</v>
+        <v>2.1141</v>
       </c>
       <c r="N33" t="n">
-        <v>362</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.1141</v>
+        <v>2.1136</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6795</v>
+        <v>0.6793</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4327</v>
+        <v>0.3981</v>
       </c>
       <c r="E34" t="n">
-        <v>2.1141</v>
+        <v>2.1136</v>
       </c>
       <c r="F34" t="n">
-        <v>3.1141</v>
+        <v>3.2069</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-1.0933</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1141</v>
+        <v>3.2069</v>
       </c>
       <c r="I34" t="n">
-        <v>3.1141</v>
+        <v>3.2339</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-1.0933</v>
       </c>
       <c r="K34" t="n">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="L34" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="M34" t="n">
-        <v>2.1141</v>
+        <v>2.1406</v>
       </c>
       <c r="N34" t="n">
-        <v>256</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35">
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.0853</v>
+        <v>2.0813</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6702</v>
+        <v>0.669</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4211</v>
+        <v>0.3853</v>
       </c>
       <c r="E35" t="n">
-        <v>2.0853</v>
+        <v>2.0813</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0645</v>
+        <v>1.0605</v>
       </c>
       <c r="G35" t="n">
         <v>1.0208</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0645</v>
+        <v>1.0605</v>
       </c>
       <c r="I35" t="n">
         <v>1.0694</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.0633</v>
+        <v>2.0581</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6632</v>
+        <v>0.6615</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4122</v>
+        <v>0.376</v>
       </c>
       <c r="E36" t="n">
-        <v>2.0633</v>
+        <v>2.0581</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3699</v>
+        <v>1.3647</v>
       </c>
       <c r="G36" t="n">
         <v>0.6934</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3699</v>
+        <v>1.3647</v>
       </c>
       <c r="I36" t="n">
         <v>1.3762</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.0144</v>
+        <v>2.0064</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6475</v>
+        <v>0.6449</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3924</v>
+        <v>0.3554</v>
       </c>
       <c r="E37" t="n">
-        <v>2.0144</v>
+        <v>2.0064</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1315</v>
+        <v>2.1235</v>
       </c>
       <c r="G37" t="n">
         <v>-0.1171</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1315</v>
+        <v>2.1235</v>
       </c>
       <c r="I37" t="n">
         <v>2.1414</v>
@@ -2158,7 +2158,7 @@
         <v>0.5886</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3185</v>
+        <v>0.2857</v>
       </c>
       <c r="E38" t="n">
         <v>1.8314</v>
@@ -2204,7 +2204,7 @@
         <v>0.4841</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1871</v>
+        <v>0.1561</v>
       </c>
       <c r="E39" t="n">
         <v>1.5061</v>
@@ -2250,7 +2250,7 @@
         <v>0.4189</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1051</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E40" t="n">
         <v>1.3033</v>
@@ -2296,7 +2296,7 @@
         <v>0.3735</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0481</v>
+        <v>0.0191</v>
       </c>
       <c r="E41" t="n">
         <v>1.1622</v>
@@ -2342,7 +2342,7 @@
         <v>0.3641</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0362</v>
+        <v>0.0074</v>
       </c>
       <c r="E42" t="n">
         <v>1.1327</v>
@@ -2388,7 +2388,7 @@
         <v>0.351</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0198</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="E43" t="n">
         <v>1.0921</v>
@@ -2434,7 +2434,7 @@
         <v>0.3172</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0227</v>
+        <v>-0.0507</v>
       </c>
       <c r="E44" t="n">
         <v>0.9869</v>
@@ -2480,7 +2480,7 @@
         <v>0.2951</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0505</v>
+        <v>-0.0781</v>
       </c>
       <c r="E45" t="n">
         <v>0.9181</v>
@@ -2526,7 +2526,7 @@
         <v>0.2704</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0815</v>
+        <v>-0.1088</v>
       </c>
       <c r="E46" t="n">
         <v>0.8411999999999999</v>
@@ -2572,7 +2572,7 @@
         <v>0.2697</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0824</v>
+        <v>-0.1096</v>
       </c>
       <c r="E47" t="n">
         <v>0.8391</v>
@@ -2618,7 +2618,7 @@
         <v>0.2349</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1261</v>
+        <v>-0.1528</v>
       </c>
       <c r="E48" t="n">
         <v>0.7308</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6958</v>
+        <v>0.6924</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2236</v>
+        <v>0.2225</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1403</v>
+        <v>-0.1681</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6958</v>
+        <v>0.6924</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9185</v>
+        <v>0.9151</v>
       </c>
       <c r="G49" t="n">
         <v>-0.2227</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9185</v>
+        <v>0.9151</v>
       </c>
       <c r="I49" t="n">
         <v>0.9228</v>
@@ -2710,7 +2710,7 @@
         <v>0.1906</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1818</v>
+        <v>-0.2077</v>
       </c>
       <c r="E50" t="n">
         <v>0.5929</v>
@@ -2756,7 +2756,7 @@
         <v>0.1813</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1935</v>
+        <v>-0.2192</v>
       </c>
       <c r="E51" t="n">
         <v>0.5639999999999999</v>
@@ -2802,7 +2802,7 @@
         <v>0.1606</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2195</v>
+        <v>-0.2448</v>
       </c>
       <c r="E52" t="n">
         <v>0.4998</v>
@@ -2848,7 +2848,7 @@
         <v>0.1325</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2548</v>
+        <v>-0.2796</v>
       </c>
       <c r="E53" t="n">
         <v>0.4124</v>
@@ -2894,7 +2894,7 @@
         <v>0.1083</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2853</v>
+        <v>-0.3097</v>
       </c>
       <c r="E54" t="n">
         <v>0.3368</v>
@@ -2940,7 +2940,7 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3011</v>
+        <v>-0.3253</v>
       </c>
       <c r="E55" t="n">
         <v>0.2978</v>
@@ -2986,7 +2986,7 @@
         <v>0.0605</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3454</v>
+        <v>-0.369</v>
       </c>
       <c r="E56" t="n">
         <v>0.1881</v>
@@ -3032,7 +3032,7 @@
         <v>0.0589</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3474</v>
+        <v>-0.3709</v>
       </c>
       <c r="E57" t="n">
         <v>0.1832</v>
@@ -3078,7 +3078,7 @@
         <v>0.0504</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.3581</v>
+        <v>-0.3815</v>
       </c>
       <c r="E58" t="n">
         <v>0.1567</v>
@@ -3124,7 +3124,7 @@
         <v>0.0455</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.3641</v>
+        <v>-0.3875</v>
       </c>
       <c r="E59" t="n">
         <v>0.1417</v>
@@ -3170,7 +3170,7 @@
         <v>0.017</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4</v>
+        <v>-0.4228</v>
       </c>
       <c r="E60" t="n">
         <v>0.0529</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1624</v>
+        <v>-0.1643</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0522</v>
+        <v>-0.0528</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.487</v>
+        <v>-0.5094</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1624</v>
+        <v>-0.1643</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4975</v>
+        <v>0.4956</v>
       </c>
       <c r="G61" t="n">
         <v>-0.6599</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4975</v>
+        <v>0.4956</v>
       </c>
       <c r="I61" t="n">
         <v>0.4998</v>
@@ -3262,7 +3262,7 @@
         <v>-0.077</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5182</v>
+        <v>-0.5394</v>
       </c>
       <c r="E62" t="n">
         <v>-0.2397</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2487</v>
+        <v>-0.2486</v>
       </c>
       <c r="C63" t="n">
         <v>-0.0799</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5218</v>
+        <v>-0.543</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2487</v>
+        <v>-0.2486</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.0219</v>
+        <v>-0.0218</v>
       </c>
       <c r="G63" t="n">
         <v>-0.2268</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.0219</v>
+        <v>-0.0218</v>
       </c>
       <c r="I63" t="n">
         <v>-0.022</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1016</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5491</v>
+        <v>-0.5698</v>
       </c>
       <c r="E64" t="n">
         <v>-0.3161</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3511</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8626</v>
+        <v>-0.8791</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0923</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3831</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9028</v>
+        <v>-0.9187</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1918</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3872</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.908</v>
+        <v>-0.9238</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2046</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4258</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9566</v>
+        <v>-0.9717</v>
       </c>
       <c r="E68" t="n">
         <v>-1.3248</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4747</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.018</v>
+        <v>-1.0323</v>
       </c>
       <c r="E69" t="n">
         <v>-1.477</v>
@@ -3630,7 +3630,7 @@
         <v>-0.505</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0561</v>
+        <v>-1.0699</v>
       </c>
       <c r="E70" t="n">
         <v>-1.5713</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5683</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1357</v>
+        <v>-1.1484</v>
       </c>
       <c r="E71" t="n">
         <v>-1.7682</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6259</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.2081</v>
+        <v>-1.2198</v>
       </c>
       <c r="E72" t="n">
         <v>-1.9474</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6629</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2546</v>
+        <v>-1.2656</v>
       </c>
       <c r="E73" t="n">
         <v>-2.0625</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-2.2826</v>
+        <v>-2.2756</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7337</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3435</v>
+        <v>-1.3505</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.2826</v>
+        <v>-2.2756</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.8829</v>
+        <v>-1.8759</v>
       </c>
       <c r="G74" t="n">
         <v>-0.3997</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.8829</v>
+        <v>-1.8759</v>
       </c>
       <c r="I74" t="n">
         <v>-1.8917</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7756999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3963</v>
+        <v>-1.4054</v>
       </c>
       <c r="E75" t="n">
         <v>-2.4133</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9076</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5621</v>
+        <v>-1.5689</v>
       </c>
       <c r="E76" t="n">
         <v>-2.8238</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9246</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5834</v>
+        <v>-1.5899</v>
       </c>
       <c r="E77" t="n">
         <v>-2.8766</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9592000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.627</v>
+        <v>-1.6329</v>
       </c>
       <c r="E78" t="n">
         <v>-2.9843</v>
@@ -4044,7 +4044,7 @@
         <v>-1.2009</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9308</v>
+        <v>-1.9325</v>
       </c>
       <c r="E79" t="n">
         <v>-3.7364</v>
@@ -4090,7 +4090,7 @@
         <v>-1.2816</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.0322</v>
+        <v>-2.0325</v>
       </c>
       <c r="E80" t="n">
         <v>-3.9875</v>
@@ -4136,7 +4136,7 @@
         <v>-1.3023</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0582</v>
+        <v>-2.0581</v>
       </c>
       <c r="E81" t="n">
         <v>-4.0518</v>

--- a/database/event/8044/event_8044_evp_summary.xlsx
+++ b/database/event/8044/event_8044_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2131</v>
+        <v>7.4924</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3184</v>
+        <v>2.4081</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6593</v>
+        <v>2.7329</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2131</v>
+        <v>7.4924</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3377</v>
+        <v>3.3423</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8754</v>
+        <v>3.8436</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5803</v>
+        <v>4.5902</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6983</v>
+        <v>4.7085</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8754</v>
+        <v>3.8436</v>
       </c>
       <c r="K2" t="n">
         <v>279</v>
@@ -529,7 +529,7 @@
         <v>101</v>
       </c>
       <c r="M2" t="n">
-        <v>8.573699999999999</v>
+        <v>8.552099999999999</v>
       </c>
       <c r="N2" t="n">
         <v>380</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8539</v>
+        <v>7.1036</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2029</v>
+        <v>2.2832</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4958</v>
+        <v>2.5592</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8539</v>
+        <v>7.1036</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>3.4796</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2469</v>
+        <v>3.2953</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9809</v>
+        <v>4.8908</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9809</v>
+        <v>4.8908</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2469</v>
+        <v>3.2953</v>
       </c>
       <c r="K3" t="n">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="L3" t="n">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2278</v>
+        <v>8.1861</v>
       </c>
       <c r="N3" t="n">
-        <v>422</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7749</v>
+        <v>6.9834</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1775</v>
+        <v>2.2445</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4599</v>
+        <v>2.5055</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7749</v>
+        <v>6.9834</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4796</v>
+        <v>2.607</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2953</v>
+        <v>4.2283</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8908</v>
+        <v>2.9809</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8908</v>
+        <v>2.9809</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2953</v>
+        <v>4.2283</v>
       </c>
       <c r="K4" t="n">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="L4" t="n">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1861</v>
+        <v>7.2092</v>
       </c>
       <c r="N4" t="n">
-        <v>309</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5209</v>
+        <v>6.6962</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0959</v>
+        <v>2.1522</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3442</v>
+        <v>2.3772</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5209</v>
+        <v>6.6962</v>
       </c>
       <c r="F5" t="n">
         <v>4.4486</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0723</v>
+        <v>2.0836</v>
       </c>
       <c r="H5" t="n">
         <v>7.0117</v>
@@ -658,7 +658,7 @@
         <v>7.0117</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0723</v>
+        <v>2.0836</v>
       </c>
       <c r="K5" t="n">
         <v>233</v>
@@ -667,7 +667,7 @@
         <v>189</v>
       </c>
       <c r="M5" t="n">
-        <v>9.084</v>
+        <v>9.0953</v>
       </c>
       <c r="N5" t="n">
         <v>422</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.364</v>
+        <v>6.5099</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0455</v>
+        <v>2.0924</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2728</v>
+        <v>2.294</v>
       </c>
       <c r="E6" t="n">
-        <v>6.364</v>
+        <v>6.5099</v>
       </c>
       <c r="F6" t="n">
         <v>2.8126</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8984</v>
+        <v>5.9917</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8958</v>
+        <v>1.9258</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0609</v>
+        <v>2.0625</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8984</v>
+        <v>5.9917</v>
       </c>
       <c r="F7" t="n">
         <v>2.1679</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7305</v>
+        <v>3.6711</v>
       </c>
       <c r="H7" t="n">
         <v>2.1679</v>
@@ -750,7 +750,7 @@
         <v>2.1679</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7305</v>
+        <v>3.6711</v>
       </c>
       <c r="K7" t="n">
         <v>233</v>
@@ -759,7 +759,7 @@
         <v>189</v>
       </c>
       <c r="M7" t="n">
-        <v>5.898400000000001</v>
+        <v>5.839</v>
       </c>
       <c r="N7" t="n">
         <v>422</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5597</v>
+        <v>5.6928</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7869</v>
+        <v>1.8297</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9067</v>
+        <v>1.929</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5597</v>
+        <v>5.6928</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2737</v>
+        <v>4.2657</v>
       </c>
       <c r="G8" t="n">
-        <v>1.286</v>
+        <v>1.2871</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6288</v>
+        <v>6.6113</v>
       </c>
       <c r="I8" t="n">
-        <v>6.7996</v>
+        <v>6.7817</v>
       </c>
       <c r="J8" t="n">
-        <v>1.286</v>
+        <v>1.2871</v>
       </c>
       <c r="K8" t="n">
         <v>279</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>8.085599999999999</v>
+        <v>8.0688</v>
       </c>
       <c r="N8" t="n">
         <v>380</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.4136</v>
+        <v>5.3931</v>
       </c>
       <c r="C9" t="n">
-        <v>1.74</v>
+        <v>1.7334</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8402</v>
+        <v>1.7952</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4136</v>
+        <v>5.3931</v>
       </c>
       <c r="F9" t="n">
         <v>3.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3736</v>
+        <v>2.3741</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9286</v>
+        <v>3.9288</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0298</v>
+        <v>4.03</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3736</v>
+        <v>2.3741</v>
       </c>
       <c r="K9" t="n">
         <v>253</v>
@@ -851,7 +851,7 @@
         <v>109</v>
       </c>
       <c r="M9" t="n">
-        <v>6.4034</v>
+        <v>6.4041</v>
       </c>
       <c r="N9" t="n">
         <v>362</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.6151</v>
+        <v>4.8057</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4833</v>
+        <v>1.5446</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4767</v>
+        <v>1.5328</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6151</v>
+        <v>4.8057</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1895</v>
+        <v>3.1435</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4256</v>
+        <v>1.4085</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1895</v>
+        <v>4.1551</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1895</v>
+        <v>4.2622</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4256</v>
+        <v>1.4085</v>
       </c>
       <c r="K10" t="n">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="L10" t="n">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6151</v>
+        <v>5.6707</v>
       </c>
       <c r="N10" t="n">
-        <v>422</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.5514</v>
+        <v>4.6926</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4629</v>
+        <v>1.5083</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4477</v>
+        <v>1.4823</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5514</v>
+        <v>4.6926</v>
       </c>
       <c r="F11" t="n">
-        <v>3.143</v>
+        <v>3.9058</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4084</v>
+        <v>0.5242</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1542</v>
+        <v>5.8237</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2612</v>
+        <v>5.9738</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4084</v>
+        <v>0.5242</v>
       </c>
       <c r="K11" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="L11" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="M11" t="n">
-        <v>5.6696</v>
+        <v>6.497999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>362</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4234</v>
+        <v>4.4694</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4217</v>
+        <v>1.4365</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3894</v>
+        <v>1.3826</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4234</v>
+        <v>4.4694</v>
       </c>
       <c r="F12" t="n">
-        <v>3.899</v>
+        <v>1.1895</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5244</v>
+        <v>3.4257</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8087</v>
+        <v>1.1895</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9584</v>
+        <v>1.1895</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5244</v>
+        <v>3.4257</v>
       </c>
       <c r="K12" t="n">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L12" t="n">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="M12" t="n">
-        <v>6.4828</v>
+        <v>4.6152</v>
       </c>
       <c r="N12" t="n">
-        <v>313</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8573</v>
+        <v>4.1829</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2398</v>
+        <v>1.3444</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1317</v>
+        <v>1.2546</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8573</v>
+        <v>4.1829</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8573</v>
+        <v>3.8577</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7174</v>
+        <v>5.7183</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7174</v>
+        <v>5.7183</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.7174</v>
+        <v>5.7183</v>
       </c>
       <c r="N13" t="n">
         <v>287</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8505</v>
+        <v>3.9104</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2376</v>
+        <v>1.2568</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1286</v>
+        <v>1.1329</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8505</v>
+        <v>3.9104</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8505</v>
+        <v>3.2233</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.5268</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7027</v>
+        <v>4.3298</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7027</v>
+        <v>4.3298</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.5268</v>
       </c>
       <c r="K14" t="n">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
-        <v>5.7027</v>
+        <v>4.856599999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>287</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7754</v>
+        <v>3.8998</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2135</v>
+        <v>1.2534</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0944</v>
+        <v>1.1281</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7754</v>
+        <v>3.8998</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2486</v>
+        <v>3.8468</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5268</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3852</v>
+        <v>5.6946</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3852</v>
+        <v>5.6946</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5268</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.912</v>
+        <v>5.6946</v>
       </c>
       <c r="N15" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.7385</v>
+        <v>3.8604</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2016</v>
+        <v>1.2408</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0776</v>
+        <v>1.1105</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7385</v>
+        <v>3.8604</v>
       </c>
       <c r="F16" t="n">
-        <v>3.04</v>
+        <v>3.327</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6985</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9286</v>
+        <v>4.5568</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9286</v>
+        <v>4.5568</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6985</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6271</v>
+        <v>4.5568</v>
       </c>
       <c r="N16" t="n">
-        <v>256</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.5533</v>
+        <v>3.8436</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1421</v>
+        <v>1.2354</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9933</v>
+        <v>1.103</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5533</v>
+        <v>3.8436</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4056</v>
+        <v>3.0396</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1477</v>
+        <v>0.6977</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5402</v>
+        <v>3.9277</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5402</v>
+        <v>3.9277</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1477</v>
+        <v>0.6977</v>
       </c>
       <c r="K17" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6879</v>
+        <v>4.6254</v>
       </c>
       <c r="N17" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.4585</v>
+        <v>3.6517</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1116</v>
+        <v>1.1737</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9502</v>
+        <v>1.0173</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4585</v>
+        <v>3.6517</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4585</v>
+        <v>3.4583</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8447</v>
+        <v>4.8442</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8447</v>
+        <v>4.8442</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.8447</v>
+        <v>4.8442</v>
       </c>
       <c r="N18" t="n">
         <v>276</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.4345</v>
+        <v>3.5931</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1039</v>
+        <v>1.1549</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9393</v>
+        <v>0.9911</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4345</v>
+        <v>3.5931</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3119</v>
+        <v>3.3121</v>
       </c>
       <c r="G19" t="n">
         <v>0.1226</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5238</v>
+        <v>4.5242</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5238</v>
+        <v>4.5242</v>
       </c>
       <c r="J19" t="n">
         <v>0.1226</v>
@@ -1311,7 +1311,7 @@
         <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6464</v>
+        <v>4.646800000000001</v>
       </c>
       <c r="N19" t="n">
         <v>252</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3324</v>
+        <v>3.5128</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0711</v>
+        <v>1.1291</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8928</v>
+        <v>0.9553</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3324</v>
+        <v>3.5128</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3324</v>
+        <v>2.4057</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.1477</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5687</v>
+        <v>2.5405</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5687</v>
+        <v>2.5405</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.1477</v>
       </c>
       <c r="K20" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5687</v>
+        <v>3.6882</v>
       </c>
       <c r="N20" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2685</v>
+        <v>3.4507</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0505</v>
+        <v>1.1091</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8637</v>
+        <v>0.9275</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2685</v>
+        <v>3.4507</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1615</v>
+        <v>3.1617</v>
       </c>
       <c r="G21" t="n">
         <v>0.107</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1945</v>
+        <v>4.1951</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1945</v>
+        <v>4.1951</v>
       </c>
       <c r="J21" t="n">
         <v>0.107</v>
@@ -1403,7 +1403,7 @@
         <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3015</v>
+        <v>4.3021</v>
       </c>
       <c r="N21" t="n">
         <v>252</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.2178</v>
+        <v>3.2601</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0342</v>
+        <v>1.0478</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8406</v>
+        <v>0.8424</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2178</v>
+        <v>3.2601</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5811</v>
+        <v>3.581</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3633</v>
+        <v>-0.3634</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1129</v>
+        <v>5.1128</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2447</v>
+        <v>5.2446</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3633</v>
+        <v>-0.3634</v>
       </c>
       <c r="K22" t="n">
         <v>247</v>
@@ -1449,7 +1449,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8814</v>
+        <v>4.8812</v>
       </c>
       <c r="N22" t="n">
         <v>313</v>
@@ -1458,185 +1458,185 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.0815</v>
+        <v>3.2025</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.0293</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7786</v>
+        <v>0.8167</v>
       </c>
       <c r="E23" t="n">
-        <v>3.0815</v>
+        <v>3.2025</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0815</v>
+        <v>1.8555</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.1864</v>
       </c>
       <c r="H23" t="n">
-        <v>4.0196</v>
+        <v>1.8555</v>
       </c>
       <c r="I23" t="n">
-        <v>4.0196</v>
+        <v>1.9033</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.1864</v>
       </c>
       <c r="K23" t="n">
-        <v>182</v>
+        <v>279</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M23" t="n">
-        <v>4.0196</v>
+        <v>3.0897</v>
       </c>
       <c r="N23" t="n">
-        <v>182</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.0519</v>
+        <v>3.1553</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9809</v>
+        <v>1.0141</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7651</v>
+        <v>0.7956</v>
       </c>
       <c r="E24" t="n">
-        <v>3.0519</v>
+        <v>3.1553</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8555</v>
+        <v>2.8386</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1965</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8555</v>
+        <v>3.4878</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9033</v>
+        <v>3.4878</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1965</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="L24" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.0998</v>
+        <v>3.4878</v>
       </c>
       <c r="N24" t="n">
-        <v>380</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.9317</v>
+        <v>2.9881</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9423</v>
+        <v>0.9604</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7104</v>
+        <v>0.7209</v>
       </c>
       <c r="E25" t="n">
-        <v>2.9317</v>
+        <v>2.9881</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1823</v>
+        <v>1.8783</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7494</v>
+        <v>1.0262</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1823</v>
+        <v>1.8783</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1823</v>
+        <v>1.9267</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7494</v>
+        <v>1.0262</v>
       </c>
       <c r="K25" t="n">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="L25" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9317</v>
+        <v>2.9529</v>
       </c>
       <c r="N25" t="n">
-        <v>231</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.9148</v>
+        <v>2.988</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9368</v>
+        <v>0.9604</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7027</v>
+        <v>0.7209</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9148</v>
+        <v>2.988</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8884</v>
+        <v>3.0868</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0264</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8884</v>
+        <v>4.0312</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9371</v>
+        <v>4.0312</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0264</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="L26" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9635</v>
+        <v>4.0312</v>
       </c>
       <c r="N26" t="n">
-        <v>313</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8878</v>
+        <v>2.9705</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9282</v>
+        <v>0.9548</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6904</v>
+        <v>0.713</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8878</v>
+        <v>2.9705</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9697</v>
+        <v>2.9694</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0819</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7747</v>
+        <v>3.7742</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7747</v>
+        <v>3.7742</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0819</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>210</v>
@@ -1679,7 +1679,7 @@
         <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6928</v>
+        <v>3.6921</v>
       </c>
       <c r="N27" t="n">
         <v>256</v>
@@ -1688,185 +1688,185 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8475</v>
+        <v>2.9606</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9152</v>
+        <v>0.9516</v>
       </c>
       <c r="D28" t="n">
-        <v>0.672</v>
+        <v>0.7086</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8475</v>
+        <v>2.9606</v>
       </c>
       <c r="F28" t="n">
-        <v>3.1293</v>
+        <v>2.1823</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2818</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1242</v>
+        <v>2.1823</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1242</v>
+        <v>2.1823</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2818</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="L28" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8424</v>
+        <v>2.9409</v>
       </c>
       <c r="N28" t="n">
-        <v>309</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.8382</v>
+        <v>2.8057</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9122</v>
+        <v>0.9018</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6394</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8382</v>
+        <v>2.8057</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8382</v>
+        <v>2.6607</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4869</v>
+        <v>3.0986</v>
       </c>
       <c r="I29" t="n">
-        <v>3.4869</v>
+        <v>3.0986</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4869</v>
+        <v>3.0986</v>
       </c>
       <c r="N29" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.793</v>
+        <v>2.7455</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8824</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6472</v>
+        <v>0.6125</v>
       </c>
       <c r="E30" t="n">
-        <v>2.793</v>
+        <v>2.7455</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>3.1293</v>
       </c>
       <c r="G30" t="n">
-        <v>0.593</v>
+        <v>-0.2818</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2</v>
+        <v>4.1242</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2567</v>
+        <v>4.1242</v>
       </c>
       <c r="J30" t="n">
-        <v>0.593</v>
+        <v>-0.2818</v>
       </c>
       <c r="K30" t="n">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="L30" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8497</v>
+        <v>3.8424</v>
       </c>
       <c r="N30" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.6611</v>
+        <v>2.6506</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8519</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>2.6611</v>
+        <v>2.6506</v>
       </c>
       <c r="F31" t="n">
-        <v>2.6611</v>
+        <v>2.1826</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.5739</v>
       </c>
       <c r="H31" t="n">
-        <v>3.0993</v>
+        <v>2.1826</v>
       </c>
       <c r="I31" t="n">
-        <v>3.0993</v>
+        <v>2.2388</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.5739</v>
       </c>
       <c r="K31" t="n">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M31" t="n">
-        <v>3.0993</v>
+        <v>2.8127</v>
       </c>
       <c r="N31" t="n">
-        <v>213</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.5392</v>
+        <v>2.5963</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8161</v>
+        <v>0.8345</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5317</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5392</v>
+        <v>2.5963</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5392</v>
+        <v>2.5391</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8326</v>
+        <v>2.8324</v>
       </c>
       <c r="I32" t="n">
-        <v>2.8326</v>
+        <v>2.8324</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.8326</v>
+        <v>2.8324</v>
       </c>
       <c r="N32" t="n">
         <v>276</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.4508</v>
+        <v>2.5869</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7877</v>
+        <v>0.8315</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4915</v>
+        <v>0.5417</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4508</v>
+        <v>2.5869</v>
       </c>
       <c r="F33" t="n">
         <v>2.4663</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0155</v>
+        <v>-0.0034</v>
       </c>
       <c r="H33" t="n">
-        <v>2.673</v>
+        <v>2.6729</v>
       </c>
       <c r="I33" t="n">
-        <v>2.7419</v>
+        <v>2.7418</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0155</v>
+        <v>-0.0034</v>
       </c>
       <c r="K33" t="n">
         <v>247</v>
@@ -1955,7 +1955,7 @@
         <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>2.7264</v>
+        <v>2.7384</v>
       </c>
       <c r="N33" t="n">
         <v>313</v>
@@ -1964,814 +1964,814 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.2939</v>
+        <v>2.45</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7373</v>
+        <v>0.7875</v>
       </c>
       <c r="D34" t="n">
-        <v>0.42</v>
+        <v>0.4805</v>
       </c>
       <c r="E34" t="n">
-        <v>2.2939</v>
+        <v>2.45</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4369</v>
+        <v>3.2576</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.143</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.6086</v>
+        <v>4.4049</v>
       </c>
       <c r="I34" t="n">
-        <v>2.6758</v>
+        <v>4.4049</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.143</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L34" t="n">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5328</v>
+        <v>3.4049</v>
       </c>
       <c r="N34" t="n">
-        <v>362</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.2688</v>
+        <v>2.3697</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7292</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4086</v>
+        <v>0.4447</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2688</v>
+        <v>2.3697</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2688</v>
+        <v>2.8505</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-0.6552</v>
       </c>
       <c r="H35" t="n">
-        <v>4.4294</v>
+        <v>3.5139</v>
       </c>
       <c r="I35" t="n">
-        <v>4.4294</v>
+        <v>3.6045</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.6552</v>
       </c>
       <c r="K35" t="n">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="L35" t="n">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4294</v>
+        <v>2.9493</v>
       </c>
       <c r="N35" t="n">
-        <v>231</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2015</v>
+        <v>2.2716</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7076</v>
+        <v>0.7301</v>
       </c>
       <c r="D36" t="n">
-        <v>0.378</v>
+        <v>0.4009</v>
       </c>
       <c r="E36" t="n">
-        <v>2.2015</v>
+        <v>2.2716</v>
       </c>
       <c r="F36" t="n">
-        <v>2.9976</v>
+        <v>2.4313</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7961</v>
+        <v>-0.1613</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8358</v>
+        <v>2.5964</v>
       </c>
       <c r="I36" t="n">
-        <v>3.8358</v>
+        <v>2.6633</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7961</v>
+        <v>-0.1613</v>
       </c>
       <c r="K36" t="n">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="L36" t="n">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="M36" t="n">
-        <v>3.0397</v>
+        <v>2.502</v>
       </c>
       <c r="N36" t="n">
-        <v>231</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.195</v>
+        <v>2.1309</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7055</v>
+        <v>0.6849</v>
       </c>
       <c r="D37" t="n">
-        <v>0.375</v>
+        <v>0.338</v>
       </c>
       <c r="E37" t="n">
-        <v>2.195</v>
+        <v>2.1309</v>
       </c>
       <c r="F37" t="n">
-        <v>2.8504</v>
+        <v>2.9976</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6554</v>
+        <v>-0.7975</v>
       </c>
       <c r="H37" t="n">
-        <v>3.5138</v>
+        <v>3.8358</v>
       </c>
       <c r="I37" t="n">
-        <v>3.6043</v>
+        <v>3.8358</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6554</v>
+        <v>-0.7975</v>
       </c>
       <c r="K37" t="n">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L37" t="n">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9489</v>
+        <v>3.0383</v>
       </c>
       <c r="N37" t="n">
-        <v>362</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.1268</v>
+        <v>2.1238</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6836</v>
+        <v>0.6826</v>
       </c>
       <c r="D38" t="n">
-        <v>0.344</v>
+        <v>0.3348</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1268</v>
+        <v>2.1238</v>
       </c>
       <c r="F38" t="n">
-        <v>2.7858</v>
+        <v>1.9928</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.659</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3723</v>
+        <v>1.9928</v>
       </c>
       <c r="I38" t="n">
-        <v>3.3723</v>
+        <v>1.9928</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.659</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L38" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7133</v>
+        <v>1.9928</v>
       </c>
       <c r="N38" t="n">
-        <v>309</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.0065</v>
+        <v>2.1121</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6449</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2892</v>
+        <v>0.3296</v>
       </c>
       <c r="E39" t="n">
-        <v>2.0065</v>
+        <v>2.1121</v>
       </c>
       <c r="F39" t="n">
-        <v>2.923</v>
+        <v>1.9149</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9165</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.6726</v>
+        <v>1.9149</v>
       </c>
       <c r="I39" t="n">
-        <v>3.6726</v>
+        <v>1.9149</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9165</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.7561</v>
+        <v>1.9149</v>
       </c>
       <c r="N39" t="n">
-        <v>256</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9928</v>
+        <v>2.032</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6405</v>
+        <v>0.6531</v>
       </c>
       <c r="D40" t="n">
-        <v>0.283</v>
+        <v>0.2938</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9928</v>
+        <v>2.032</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9928</v>
+        <v>2.7858</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.659</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9928</v>
+        <v>3.3723</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9928</v>
+        <v>3.3723</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.659</v>
       </c>
       <c r="K40" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9928</v>
+        <v>2.7133</v>
       </c>
       <c r="N40" t="n">
-        <v>147</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.9151</v>
+        <v>1.9697</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6155</v>
+        <v>0.6331</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2476</v>
+        <v>0.266</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9151</v>
+        <v>1.9697</v>
       </c>
       <c r="F41" t="n">
-        <v>1.9151</v>
+        <v>2.9225</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.9167</v>
       </c>
       <c r="H41" t="n">
-        <v>1.9151</v>
+        <v>3.6715</v>
       </c>
       <c r="I41" t="n">
-        <v>1.9151</v>
+        <v>3.6715</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.9167</v>
       </c>
       <c r="K41" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>1.9151</v>
+        <v>2.7548</v>
       </c>
       <c r="N41" t="n">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.8394</v>
+        <v>1.93</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6203</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2131</v>
+        <v>0.2483</v>
       </c>
       <c r="E42" t="n">
-        <v>1.8394</v>
+        <v>1.93</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8394</v>
+        <v>1.5007</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.4266</v>
       </c>
       <c r="H42" t="n">
-        <v>1.8394</v>
+        <v>1.5007</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8394</v>
+        <v>1.5007</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.4266</v>
       </c>
       <c r="K42" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8394</v>
+        <v>1.9273</v>
       </c>
       <c r="N42" t="n">
-        <v>193</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.801</v>
+        <v>1.918</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5789</v>
+        <v>0.6165</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1956</v>
+        <v>0.2429</v>
       </c>
       <c r="E43" t="n">
-        <v>1.801</v>
+        <v>1.918</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3961</v>
+        <v>1.8394</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4049</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.3961</v>
+        <v>1.8394</v>
       </c>
       <c r="I43" t="n">
-        <v>1.3961</v>
+        <v>1.8394</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4049</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="L43" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.801</v>
+        <v>1.8394</v>
       </c>
       <c r="N43" t="n">
-        <v>256</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.7819</v>
+        <v>1.8235</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5727</v>
+        <v>0.5861</v>
       </c>
       <c r="D44" t="n">
-        <v>0.187</v>
+        <v>0.2007</v>
       </c>
       <c r="E44" t="n">
-        <v>1.7819</v>
+        <v>1.8235</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7819</v>
+        <v>1.6202</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7819</v>
+        <v>1.6202</v>
       </c>
       <c r="I44" t="n">
-        <v>1.7819</v>
+        <v>1.6202</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7819</v>
+        <v>1.6202</v>
       </c>
       <c r="N44" t="n">
-        <v>287</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.6974</v>
+        <v>1.8048</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5456</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1485</v>
+        <v>0.1923</v>
       </c>
       <c r="E45" t="n">
-        <v>1.6974</v>
+        <v>1.8048</v>
       </c>
       <c r="F45" t="n">
-        <v>1.6974</v>
+        <v>1.7829</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.6974</v>
+        <v>1.7829</v>
       </c>
       <c r="I45" t="n">
-        <v>1.6974</v>
+        <v>1.7829</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.6974</v>
+        <v>1.7829</v>
       </c>
       <c r="N45" t="n">
-        <v>231</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Demho</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.6889</v>
+        <v>1.7253</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5545</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1446</v>
+        <v>0.1568</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6889</v>
+        <v>1.7253</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6889</v>
+        <v>1.4917</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.6889</v>
+        <v>1.4917</v>
       </c>
       <c r="I46" t="n">
-        <v>1.6889</v>
+        <v>1.4917</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.6889</v>
+        <v>1.4917</v>
       </c>
       <c r="N46" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.5883</v>
+        <v>1.6835</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5105</v>
+        <v>0.5411</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0988</v>
+        <v>0.1382</v>
       </c>
       <c r="E47" t="n">
-        <v>1.5883</v>
+        <v>1.6835</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5883</v>
+        <v>1.6816</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5883</v>
+        <v>1.6816</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5883</v>
+        <v>1.6816</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.5883</v>
+        <v>1.6816</v>
       </c>
       <c r="N47" t="n">
-        <v>130</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5114</v>
+        <v>1.4802</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4858</v>
+        <v>0.4758</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0638</v>
+        <v>0.0474</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5114</v>
+        <v>1.4802</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5114</v>
+        <v>1.4827</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5114</v>
+        <v>1.4827</v>
       </c>
       <c r="I48" t="n">
-        <v>1.5114</v>
+        <v>1.4827</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>276</v>
+        <v>147</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.5114</v>
+        <v>1.4827</v>
       </c>
       <c r="N48" t="n">
-        <v>276</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Demho</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.4917</v>
+        <v>1.4496</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4794</v>
+        <v>0.4659</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0548</v>
+        <v>0.0337</v>
       </c>
       <c r="E49" t="n">
-        <v>1.4917</v>
+        <v>1.4496</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4917</v>
+        <v>1.6975</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.4917</v>
+        <v>1.6975</v>
       </c>
       <c r="I49" t="n">
-        <v>1.4917</v>
+        <v>1.6975</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4917</v>
+        <v>1.6975</v>
       </c>
       <c r="N49" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.4827</v>
+        <v>1.3501</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4766</v>
+        <v>0.4339</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0508</v>
+        <v>-0.0108</v>
       </c>
       <c r="E50" t="n">
-        <v>1.4827</v>
+        <v>1.3501</v>
       </c>
       <c r="F50" t="n">
-        <v>1.4827</v>
+        <v>1.371</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.4827</v>
+        <v>1.371</v>
       </c>
       <c r="I50" t="n">
-        <v>1.4827</v>
+        <v>1.371</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.4827</v>
+        <v>1.371</v>
       </c>
       <c r="N50" t="n">
-        <v>147</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.327</v>
+        <v>1.3395</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4265</v>
+        <v>0.4305</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0201</v>
+        <v>-0.0155</v>
       </c>
       <c r="E51" t="n">
-        <v>1.327</v>
+        <v>1.3395</v>
       </c>
       <c r="F51" t="n">
-        <v>1.327</v>
+        <v>1.5112</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.327</v>
+        <v>1.5112</v>
       </c>
       <c r="I51" t="n">
-        <v>1.327</v>
+        <v>1.5112</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.327</v>
+        <v>1.5112</v>
       </c>
       <c r="N51" t="n">
         <v>276</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.1865</v>
+        <v>1.2555</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3814</v>
+        <v>0.4035</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.053</v>
       </c>
       <c r="E52" t="n">
-        <v>1.1865</v>
+        <v>1.2555</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1865</v>
+        <v>1.1862</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1865</v>
+        <v>1.1862</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1865</v>
+        <v>1.1862</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1865</v>
+        <v>1.1862</v>
       </c>
       <c r="N52" t="n">
         <v>213</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.1668</v>
+        <v>1.1928</v>
       </c>
       <c r="C53" t="n">
-        <v>0.375</v>
+        <v>0.3834</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0931</v>
+        <v>-0.081</v>
       </c>
       <c r="E53" t="n">
-        <v>1.1668</v>
+        <v>1.1928</v>
       </c>
       <c r="F53" t="n">
-        <v>1.1668</v>
+        <v>1.15</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.1668</v>
+        <v>1.15</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1668</v>
+        <v>1.15</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1.1668</v>
+        <v>1.15</v>
       </c>
       <c r="N53" t="n">
         <v>231</v>
@@ -2884,354 +2884,354 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9895</v>
       </c>
       <c r="C54" t="n">
         <v>0.318</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1738</v>
+        <v>-0.1718</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9895</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="N54" t="n">
-        <v>231</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9784</v>
+        <v>0.8446</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3145</v>
+        <v>0.2715</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.1788</v>
+        <v>-0.2366</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9784</v>
+        <v>0.8446</v>
       </c>
       <c r="F55" t="n">
-        <v>1.5754</v>
+        <v>1.0657</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.597</v>
+        <v>-0.3242</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5754</v>
+        <v>1.0657</v>
       </c>
       <c r="I55" t="n">
-        <v>1.616</v>
+        <v>1.0657</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.597</v>
+        <v>-0.3242</v>
       </c>
       <c r="K55" t="n">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L55" t="n">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="M55" t="n">
-        <v>1.019</v>
+        <v>0.7415</v>
       </c>
       <c r="N55" t="n">
-        <v>362</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9648</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3101</v>
+        <v>0.2662</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.185</v>
+        <v>-0.2439</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9648</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9648</v>
+        <v>0.7026</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9648</v>
+        <v>0.7026</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9648</v>
+        <v>0.7026</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.9648</v>
+        <v>0.7026</v>
       </c>
       <c r="N56" t="n">
-        <v>147</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9152</v>
+        <v>0.7683</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2942</v>
+        <v>0.2469</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.2076</v>
+        <v>-0.2706</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9152</v>
+        <v>0.7683</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8209</v>
+        <v>0.974</v>
       </c>
       <c r="G57" t="n">
-        <v>0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8209</v>
+        <v>0.974</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8421</v>
+        <v>0.974</v>
       </c>
       <c r="J57" t="n">
-        <v>0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="L57" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9363999999999999</v>
+        <v>0.974</v>
       </c>
       <c r="N57" t="n">
-        <v>380</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7861</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2527</v>
+        <v>0.2428</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.2664</v>
+        <v>-0.2764</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7861</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1.5355</v>
+        <v>1.5756</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.7494</v>
+        <v>-0.5969</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5355</v>
+        <v>1.5756</v>
       </c>
       <c r="I58" t="n">
-        <v>1.5355</v>
+        <v>1.6162</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.7494</v>
+        <v>-0.5969</v>
       </c>
       <c r="K58" t="n">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="L58" t="n">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7861000000000001</v>
+        <v>1.0193</v>
       </c>
       <c r="N58" t="n">
-        <v>231</v>
+        <v>362</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7224</v>
+        <v>0.7431</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2322</v>
+        <v>0.2388</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.2954</v>
+        <v>-0.2819</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7224</v>
+        <v>0.7431</v>
       </c>
       <c r="F59" t="n">
-        <v>1.0657</v>
+        <v>0.8214</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3433</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>1.0657</v>
+        <v>0.8214</v>
       </c>
       <c r="I59" t="n">
-        <v>1.0657</v>
+        <v>0.8426</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.3433</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>200</v>
+        <v>279</v>
       </c>
       <c r="L59" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7224000000000002</v>
+        <v>0.9383</v>
       </c>
       <c r="N59" t="n">
-        <v>231</v>
+        <v>380</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6956</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2263</v>
+        <v>0.2236</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.3037</v>
+        <v>-0.3031</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6956</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0269</v>
+        <v>1.5565</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6772</v>
+        <v>-0.7501</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0269</v>
+        <v>1.5565</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0269</v>
+        <v>1.5565</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6772</v>
+        <v>-0.7501</v>
       </c>
       <c r="K60" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="L60" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="M60" t="n">
-        <v>0.7041000000000001</v>
+        <v>0.8064</v>
       </c>
       <c r="N60" t="n">
-        <v>309</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7026</v>
+        <v>0.4799</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2258</v>
+        <v>0.1542</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3044</v>
+        <v>-0.3995</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7026</v>
+        <v>0.4799</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7026</v>
+        <v>0.6552</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.7026</v>
+        <v>0.6552</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7026</v>
+        <v>0.6552</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7026</v>
+        <v>0.6552</v>
       </c>
       <c r="N61" t="n">
         <v>193</v>
@@ -3252,47 +3252,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6552</v>
+        <v>0.4572</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2106</v>
+        <v>0.1469</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3259</v>
+        <v>-0.4096</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6552</v>
+        <v>0.4572</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6552</v>
+        <v>0.0269</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.6772</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6552</v>
+        <v>0.0269</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6552</v>
+        <v>0.0269</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>0.6772</v>
       </c>
       <c r="K62" t="n">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6552</v>
+        <v>0.7041000000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>193</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63">
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6279</v>
+        <v>0.3488</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2018</v>
+        <v>0.1121</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3384</v>
+        <v>-0.458</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6279</v>
+        <v>0.3488</v>
       </c>
       <c r="F63" t="n">
-        <v>1.6279</v>
+        <v>1.6285</v>
       </c>
       <c r="G63" t="n">
         <v>-1</v>
       </c>
       <c r="H63" t="n">
-        <v>1.6279</v>
+        <v>1.6285</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6279</v>
+        <v>1.6285</v>
       </c>
       <c r="J63" t="n">
         <v>-1</v>
@@ -3335,7 +3335,7 @@
         <v>60</v>
       </c>
       <c r="M63" t="n">
-        <v>0.6278999999999999</v>
+        <v>0.6285000000000001</v>
       </c>
       <c r="N63" t="n">
         <v>252</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1046</v>
+        <v>0.063</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0336</v>
+        <v>0.0202</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5766</v>
+        <v>-0.5857</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1046</v>
+        <v>0.063</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1046</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1046</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1046</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1046</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N64" t="n">
         <v>182</v>
@@ -3394,22 +3394,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0064</v>
+        <v>-0.1176</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0021</v>
+        <v>-0.0378</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6271</v>
+        <v>-0.6663</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0064</v>
+        <v>-0.1176</v>
       </c>
       <c r="F65" t="n">
         <v>-1.1018</v>
       </c>
       <c r="G65" t="n">
-        <v>1.0954</v>
+        <v>1.1512</v>
       </c>
       <c r="H65" t="n">
         <v>-1.1018</v>
@@ -3418,7 +3418,7 @@
         <v>-1.1018</v>
       </c>
       <c r="J65" t="n">
-        <v>1.0954</v>
+        <v>1.1512</v>
       </c>
       <c r="K65" t="n">
         <v>233</v>
@@ -3427,7 +3427,7 @@
         <v>189</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.006399999999999961</v>
+        <v>0.04940000000000011</v>
       </c>
       <c r="N65" t="n">
         <v>422</v>
@@ -3436,78 +3436,78 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.17</v>
+        <v>-0.1741</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.865</v>
+        <v>-0.8558</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.5289</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6725</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.177</v>
+        <v>-0.2161</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8749</v>
+        <v>-0.9142</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6725</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6898</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6898</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6898</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5507</v>
+        <v>-0.6898</v>
       </c>
       <c r="N67" t="n">
         <v>130</v>
@@ -3528,93 +3528,93 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6758</v>
+        <v>-0.7329</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2172</v>
+        <v>-0.2356</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9318</v>
+        <v>-0.9412</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6758</v>
+        <v>-0.7329</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6758</v>
+        <v>-0.5283</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6758</v>
+        <v>-0.5283</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6758</v>
+        <v>-0.5283</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6758</v>
+        <v>-0.5283</v>
       </c>
       <c r="N68" t="n">
-        <v>182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6785</v>
+        <v>-0.7349</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2181</v>
+        <v>-0.2362</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9331</v>
+        <v>-0.9421</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6785</v>
+        <v>-0.7349</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6785</v>
+        <v>-0.6752</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6785</v>
+        <v>-0.6752</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6785</v>
+        <v>-0.6752</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6785</v>
+        <v>-0.6752</v>
       </c>
       <c r="N69" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8508</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2596</v>
+        <v>-0.2735</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9919</v>
+        <v>-0.9939</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8508</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8079</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8079</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8079</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8077</v>
+        <v>-0.8079</v>
       </c>
       <c r="N70" t="n">
         <v>130</v>
@@ -3670,31 +3670,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-1.2358</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3073</v>
+        <v>-0.3972</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0594</v>
+        <v>-1.1658</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-1.2358</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.356</v>
+        <v>-0.4164</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.6001</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.356</v>
+        <v>-0.4164</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.356</v>
+        <v>-0.4164</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.6001</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="K71" t="n">
         <v>210</v>
@@ -3703,7 +3703,7 @@
         <v>46</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-1.0167</v>
       </c>
       <c r="N71" t="n">
         <v>256</v>
@@ -3712,47 +3712,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3528</v>
+        <v>-1.4955</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4348</v>
+        <v>-0.4807</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.24</v>
+        <v>-1.2818</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3528</v>
+        <v>-1.4955</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1927</v>
+        <v>-1.452</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.1601</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1927</v>
+        <v>-1.452</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2234</v>
+        <v>-1.452</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.1601</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="L72" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3835</v>
+        <v>-1.452</v>
       </c>
       <c r="N72" t="n">
-        <v>313</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4023</v>
+        <v>-1.5643</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4507</v>
+        <v>-0.5028</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2626</v>
+        <v>-1.3126</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4023</v>
+        <v>-1.5643</v>
       </c>
       <c r="F73" t="n">
         <v>-1.4023</v>
@@ -3804,185 +3804,185 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4243</v>
+        <v>-1.6451</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4578</v>
+        <v>-0.5288</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2726</v>
+        <v>-1.3487</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4243</v>
+        <v>-1.6451</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.4243</v>
+        <v>-1.1927</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-0.1602</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.4243</v>
+        <v>-1.1927</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.4243</v>
+        <v>-1.2234</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-0.1602</v>
       </c>
       <c r="K74" t="n">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.4243</v>
+        <v>-1.3836</v>
       </c>
       <c r="N74" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>hfah</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6944</v>
+        <v>-2.1548</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5446</v>
+        <v>-0.6926</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3955</v>
+        <v>-1.5763</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6944</v>
+        <v>-2.1548</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.6944</v>
+        <v>-1.81</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.6944</v>
+        <v>-1.81</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.6944</v>
+        <v>-1.81</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.6944</v>
+        <v>-1.81</v>
       </c>
       <c r="N75" t="n">
-        <v>130</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hfah</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8098</v>
+        <v>-2.2132</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5817</v>
+        <v>-0.7113</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4481</v>
+        <v>-1.6024</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8098</v>
+        <v>-2.2132</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8098</v>
+        <v>-1.9673</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8098</v>
+        <v>-1.9673</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.8098</v>
+        <v>-1.9673</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.8098</v>
+        <v>-1.9673</v>
       </c>
       <c r="N76" t="n">
-        <v>213</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9673</v>
+        <v>-2.2338</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6323</v>
+        <v>-0.718</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5198</v>
+        <v>-1.6116</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9673</v>
+        <v>-2.2338</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9673</v>
+        <v>-1.6945</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9673</v>
+        <v>-1.6945</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.9673</v>
+        <v>-1.6945</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.9673</v>
+        <v>-1.6945</v>
       </c>
       <c r="N77" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78">
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.1292</v>
+        <v>-2.5329</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6843</v>
+        <v>-0.8141</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5935</v>
+        <v>-1.7452</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.1292</v>
+        <v>-2.5329</v>
       </c>
       <c r="F78" t="n">
         <v>-2.1292</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.7524</v>
+        <v>-3.1792</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8847</v>
+        <v>-1.0218</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8772</v>
+        <v>-2.0339</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.7524</v>
+        <v>-3.1792</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.7524</v>
+        <v>-2.9372</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.7524</v>
+        <v>-2.9372</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.7524</v>
+        <v>-2.9372</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.7524</v>
+        <v>-2.9372</v>
       </c>
       <c r="N79" t="n">
-        <v>182</v>
+        <v>287</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.9377</v>
+        <v>-3.2357</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9442</v>
+        <v>-1.04</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9615</v>
+        <v>-2.0591</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.9377</v>
+        <v>-3.2357</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.9377</v>
+        <v>-2.7521</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.9377</v>
+        <v>-2.7521</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.9377</v>
+        <v>-2.7521</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.9377</v>
+        <v>-2.7521</v>
       </c>
       <c r="N80" t="n">
-        <v>287</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81">
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.204</v>
+        <v>-3.4278</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.0298</v>
+        <v>-1.1017</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0827</v>
+        <v>-2.1449</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.204</v>
+        <v>-3.4278</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.204</v>
+        <v>-3.2041</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.204</v>
+        <v>-3.2041</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.204</v>
+        <v>-3.2041</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.204</v>
+        <v>-3.2041</v>
       </c>
       <c r="N81" t="n">
         <v>276</v>
@@ -4269,10 +4269,10 @@
         <v>1.79</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5948</v>
+        <v>1.5953</v>
       </c>
       <c r="J2" t="n">
-        <v>28.7064</v>
+        <v>28.7154</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.64</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3603</v>
+        <v>1.3608</v>
       </c>
       <c r="J3" t="n">
-        <v>24.4854</v>
+        <v>24.4944</v>
       </c>
     </row>
     <row r="4">
@@ -4346,13 +4346,13 @@
         <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8902</v>
+        <v>0.8716</v>
       </c>
       <c r="J4" t="n">
-        <v>16.0236</v>
+        <v>15.6888</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2385</v>
+        <v>0.2388</v>
       </c>
       <c r="J5" t="n">
-        <v>4.293</v>
+        <v>4.2984</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9436</v>
+        <v>-0.9434</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.9848</v>
+        <v>-16.9812</v>
       </c>
     </row>
     <row r="7">
@@ -6669,10 +6669,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6494</v>
+        <v>0.6499</v>
       </c>
       <c r="J62" t="n">
-        <v>14.2868</v>
+        <v>14.2978</v>
       </c>
     </row>
     <row r="63">
@@ -6706,13 +6706,13 @@
         <v>22</v>
       </c>
       <c r="H63" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3112</v>
+        <v>0.2929</v>
       </c>
       <c r="J63" t="n">
-        <v>6.8464</v>
+        <v>6.4438</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.96</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.5818</v>
+        <v>-1.5796</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1902</v>
+        <v>-0.19</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.1844</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4101</v>
+        <v>-0.41</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.0222</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="67">
@@ -7469,10 +7469,10 @@
         <v>1.22</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3813</v>
+        <v>0.3818</v>
       </c>
       <c r="J82" t="n">
-        <v>11.439</v>
+        <v>11.454</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1256</v>
+        <v>0.1259</v>
       </c>
       <c r="J83" t="n">
-        <v>3.768</v>
+        <v>3.777</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1183</v>
+        <v>-0.1182</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.549</v>
+        <v>-3.546</v>
       </c>
     </row>
     <row r="85">
@@ -7586,13 +7586,13 @@
         <v>30</v>
       </c>
       <c r="H85" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2259</v>
+        <v>-0.2357</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.777</v>
+        <v>-7.071</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.64</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3957</v>
+        <v>-0.3955</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.871</v>
+        <v>-11.865</v>
       </c>
     </row>
     <row r="87">
@@ -7869,10 +7869,10 @@
         <v>1.64</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1523</v>
+        <v>1.1518</v>
       </c>
       <c r="J92" t="n">
-        <v>26.5029</v>
+        <v>26.4914</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4871</v>
+        <v>0.487</v>
       </c>
       <c r="J93" t="n">
-        <v>11.2033</v>
+        <v>11.201</v>
       </c>
     </row>
     <row r="94">
@@ -7946,13 +7946,13 @@
         <v>23</v>
       </c>
       <c r="H94" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.413</v>
+        <v>0.4342</v>
       </c>
       <c r="J94" t="n">
-        <v>9.499000000000001</v>
+        <v>9.986599999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1087</v>
+        <v>0.1083</v>
       </c>
       <c r="J95" t="n">
-        <v>2.5001</v>
+        <v>2.4909</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4277</v>
+        <v>-0.4281</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.8371</v>
+        <v>-9.846299999999999</v>
       </c>
     </row>
     <row r="97">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7904</v>
+        <v>0.7896</v>
       </c>
       <c r="J117" t="n">
-        <v>17.3888</v>
+        <v>17.3712</v>
       </c>
     </row>
     <row r="118">
@@ -8906,13 +8906,13 @@
         <v>22</v>
       </c>
       <c r="H118" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1916</v>
+        <v>0.2133</v>
       </c>
       <c r="J118" t="n">
-        <v>4.2152</v>
+        <v>4.6926</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3283</v>
+        <v>-0.3285</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.2226</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3376</v>
+        <v>-0.3378</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.4272</v>
+        <v>-7.4316</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4974</v>
+        <v>-0.4976</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.9428</v>
+        <v>-10.9472</v>
       </c>
     </row>
     <row r="122">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4584</v>
+        <v>0.4582</v>
       </c>
       <c r="J127" t="n">
-        <v>10.0848</v>
+        <v>10.0804</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.25</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3638</v>
+        <v>0.3636</v>
       </c>
       <c r="J128" t="n">
-        <v>8.0036</v>
+        <v>7.9992</v>
       </c>
     </row>
     <row r="129">
@@ -9346,13 +9346,13 @@
         <v>22</v>
       </c>
       <c r="H129" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2797</v>
+        <v>0.2918</v>
       </c>
       <c r="J129" t="n">
-        <v>6.1534</v>
+        <v>6.4196</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1759</v>
+        <v>0.1758</v>
       </c>
       <c r="J130" t="n">
-        <v>3.8698</v>
+        <v>3.8676</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2735</v>
+        <v>-0.2736</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.017</v>
+        <v>-6.0192</v>
       </c>
     </row>
     <row r="132">
@@ -10266,19 +10266,19 @@
         <v>13</v>
       </c>
       <c r="H152" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2004</v>
+        <v>-0.1912</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.6052</v>
+        <v>-2.4856</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10306,19 +10306,19 @@
         <v>13</v>
       </c>
       <c r="H153" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2637</v>
+        <v>-0.2446</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.4281</v>
+        <v>-3.1798</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10349,10 +10349,10 @@
         <v>0.74</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2637</v>
+        <v>-0.2651</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.4281</v>
+        <v>-3.4463</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5421</v>
+        <v>-0.543</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.0473</v>
+        <v>-7.059</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6575</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.538399999999999</v>
+        <v>-8.547499999999999</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>2.07</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5674</v>
+        <v>1.5686</v>
       </c>
       <c r="J157" t="n">
-        <v>20.3762</v>
+        <v>20.3918</v>
       </c>
     </row>
     <row r="158">
@@ -10506,13 +10506,13 @@
         <v>13</v>
       </c>
       <c r="H158" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4102</v>
+        <v>1.377</v>
       </c>
       <c r="J158" t="n">
-        <v>18.3326</v>
+        <v>17.901</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.66</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0993</v>
+        <v>1.0998</v>
       </c>
       <c r="J159" t="n">
-        <v>14.2909</v>
+        <v>14.2974</v>
       </c>
     </row>
     <row r="160">
@@ -10586,13 +10586,13 @@
         <v>13</v>
       </c>
       <c r="H160" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8607</v>
+        <v>0.8482</v>
       </c>
       <c r="J160" t="n">
-        <v>11.1891</v>
+        <v>11.0266</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.34</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6814</v>
+        <v>0.6822</v>
       </c>
       <c r="J161" t="n">
-        <v>8.8582</v>
+        <v>8.868600000000001</v>
       </c>
     </row>
     <row r="162">
@@ -10866,13 +10866,13 @@
         <v>18</v>
       </c>
       <c r="H167" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="I167" t="n">
-        <v>2.0094</v>
+        <v>1.9995</v>
       </c>
       <c r="J167" t="n">
-        <v>36.1692</v>
+        <v>35.991</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.83</v>
       </c>
       <c r="I168" t="n">
-        <v>1.3508</v>
+        <v>1.3517</v>
       </c>
       <c r="J168" t="n">
-        <v>24.3144</v>
+        <v>24.3306</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.92</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3497</v>
+        <v>-0.3491</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.2946</v>
+        <v>-6.2838</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.9</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4041</v>
+        <v>-0.4035</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.2738</v>
+        <v>-7.263</v>
       </c>
     </row>
     <row r="171">
@@ -11026,13 +11026,13 @@
         <v>18</v>
       </c>
       <c r="H171" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8658</v>
+        <v>-0.8861</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.5844</v>
+        <v>-15.9498</v>
       </c>
     </row>
     <row r="172">
@@ -11669,10 +11669,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8145</v>
       </c>
       <c r="J187" t="n">
-        <v>16.28</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5554</v>
+        <v>0.5557</v>
       </c>
       <c r="J188" t="n">
-        <v>11.108</v>
+        <v>11.114</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1794</v>
+        <v>0.1797</v>
       </c>
       <c r="J189" t="n">
-        <v>3.588</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>1.04</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1478</v>
+        <v>0.1482</v>
       </c>
       <c r="J190" t="n">
-        <v>2.956</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="191">
@@ -11826,13 +11826,13 @@
         <v>20</v>
       </c>
       <c r="H191" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0365</v>
+        <v>-0.0229</v>
       </c>
       <c r="J191" t="n">
-        <v>0.73</v>
+        <v>-0.458</v>
       </c>
     </row>
     <row r="192">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7178</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>14.356</v>
+        <v>14.344</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6429</v>
+        <v>0.6423</v>
       </c>
       <c r="J198" t="n">
-        <v>12.858</v>
+        <v>12.846</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.26</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6123</v>
+        <v>0.6118</v>
       </c>
       <c r="J199" t="n">
-        <v>12.246</v>
+        <v>12.236</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.15</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4331</v>
+        <v>0.4326</v>
       </c>
       <c r="J200" t="n">
-        <v>8.662000000000001</v>
+        <v>8.651999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -12226,13 +12226,13 @@
         <v>20</v>
       </c>
       <c r="H201" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3507</v>
+        <v>-0.2954</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.014</v>
+        <v>-5.908</v>
       </c>
     </row>
     <row r="202">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2397</v>
+        <v>0.239</v>
       </c>
       <c r="J232" t="n">
-        <v>4.3146</v>
+        <v>4.302</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0945</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.6956</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1307</v>
+        <v>-0.1309</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.3526</v>
+        <v>-2.3562</v>
       </c>
     </row>
     <row r="235">
@@ -13586,13 +13586,13 @@
         <v>18</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.419</v>
+        <v>-0.4104</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.542</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4631</v>
+        <v>-0.4633</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.335800000000001</v>
+        <v>-8.339399999999999</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.81</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4804</v>
+        <v>1.4809</v>
       </c>
       <c r="J237" t="n">
-        <v>26.6472</v>
+        <v>26.6562</v>
       </c>
     </row>
     <row r="238">
@@ -13706,13 +13706,13 @@
         <v>18</v>
       </c>
       <c r="H238" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I238" t="n">
-        <v>0.926</v>
+        <v>0.9079</v>
       </c>
       <c r="J238" t="n">
-        <v>16.668</v>
+        <v>16.3422</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5518</v>
+        <v>0.5521</v>
       </c>
       <c r="J239" t="n">
-        <v>9.932399999999999</v>
+        <v>9.937799999999999</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.13</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3672</v>
+        <v>0.3675</v>
       </c>
       <c r="J240" t="n">
-        <v>6.6096</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.04</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1181</v>
+        <v>0.1184</v>
       </c>
       <c r="J241" t="n">
-        <v>2.1258</v>
+        <v>2.1312</v>
       </c>
     </row>
     <row r="242">
@@ -14869,10 +14869,10 @@
         <v>1.68</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3436</v>
+        <v>1.3425</v>
       </c>
       <c r="J267" t="n">
-        <v>25.5284</v>
+        <v>25.5075</v>
       </c>
     </row>
     <row r="268">
@@ -14909,16 +14909,16 @@
         <v>1.38</v>
       </c>
       <c r="I268" t="n">
-        <v>0.91</v>
+        <v>0.9091</v>
       </c>
       <c r="J268" t="n">
-        <v>17.29</v>
+        <v>17.2729</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -14946,19 +14946,19 @@
         <v>19</v>
       </c>
       <c r="H269" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4788</v>
+        <v>0.5008</v>
       </c>
       <c r="J269" t="n">
-        <v>9.097200000000001</v>
+        <v>9.5152</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -14986,13 +14986,13 @@
         <v>19</v>
       </c>
       <c r="H270" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I270" t="n">
-        <v>0.456</v>
+        <v>0.4783</v>
       </c>
       <c r="J270" t="n">
-        <v>8.664</v>
+        <v>9.0877</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.9702</v>
+        <v>-0.9708</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.4338</v>
+        <v>-18.4452</v>
       </c>
     </row>
     <row r="272">
@@ -15066,13 +15066,13 @@
         <v>22</v>
       </c>
       <c r="H272" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0099</v>
+        <v>1.0209</v>
       </c>
       <c r="J272" t="n">
-        <v>22.2178</v>
+        <v>22.4598</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3418</v>
+        <v>0.3414</v>
       </c>
       <c r="J273" t="n">
-        <v>7.5196</v>
+        <v>7.5108</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0598</v>
+        <v>-0.0599</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.3156</v>
+        <v>-1.3178</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.72</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3311</v>
+        <v>-0.3313</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.2842</v>
+        <v>-7.2886</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.68</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3678</v>
+        <v>-0.368</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.0916</v>
+        <v>-8.096</v>
       </c>
     </row>
     <row r="277">
@@ -16269,10 +16269,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6152</v>
+        <v>0.6148</v>
       </c>
       <c r="J302" t="n">
-        <v>17.2256</v>
+        <v>17.2144</v>
       </c>
     </row>
     <row r="303">
@@ -16306,13 +16306,13 @@
         <v>28</v>
       </c>
       <c r="H303" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5937</v>
+        <v>0.6148</v>
       </c>
       <c r="J303" t="n">
-        <v>16.6236</v>
+        <v>17.2144</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>1.22</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5937</v>
+        <v>0.5933</v>
       </c>
       <c r="J304" t="n">
-        <v>16.6236</v>
+        <v>16.6124</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>1.19</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5282</v>
+        <v>0.5279</v>
       </c>
       <c r="J305" t="n">
-        <v>14.7896</v>
+        <v>14.7812</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.93</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2896</v>
+        <v>-0.2899</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.1088</v>
+        <v>-8.1172</v>
       </c>
     </row>
     <row r="307">
@@ -18669,10 +18669,10 @@
         <v>1.79</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4575</v>
+        <v>1.458</v>
       </c>
       <c r="J362" t="n">
-        <v>29.15</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.43</v>
       </c>
       <c r="I363" t="n">
-        <v>0.9796</v>
+        <v>0.98</v>
       </c>
       <c r="J363" t="n">
-        <v>19.592</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.42</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9627</v>
+        <v>0.963</v>
       </c>
       <c r="J364" t="n">
-        <v>19.254</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="365">
@@ -18786,13 +18786,13 @@
         <v>20</v>
       </c>
       <c r="H365" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2385</v>
+        <v>0.2107</v>
       </c>
       <c r="J365" t="n">
-        <v>4.77</v>
+        <v>4.214</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.83</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5729</v>
+        <v>-0.5726</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.458</v>
+        <v>-11.452</v>
       </c>
     </row>
     <row r="367">
@@ -19869,10 +19869,10 @@
         <v>1.44</v>
       </c>
       <c r="I392" t="n">
-        <v>1.0079</v>
+        <v>1.0083</v>
       </c>
       <c r="J392" t="n">
-        <v>21.1659</v>
+        <v>21.1743</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.37</v>
       </c>
       <c r="I393" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.883</v>
       </c>
       <c r="J393" t="n">
-        <v>18.5346</v>
+        <v>18.543</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.24</v>
       </c>
       <c r="I394" t="n">
-        <v>0.6249</v>
+        <v>0.625</v>
       </c>
       <c r="J394" t="n">
-        <v>13.1229</v>
+        <v>13.125</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.18</v>
       </c>
       <c r="I395" t="n">
-        <v>0.4962</v>
+        <v>0.4964</v>
       </c>
       <c r="J395" t="n">
-        <v>10.4202</v>
+        <v>10.4244</v>
       </c>
     </row>
     <row r="396">
@@ -20026,13 +20026,13 @@
         <v>21</v>
       </c>
       <c r="H396" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.101</v>
+        <v>-0.1422</v>
       </c>
       <c r="J396" t="n">
-        <v>-2.121</v>
+        <v>-2.9862</v>
       </c>
     </row>
     <row r="397">
@@ -20666,13 +20666,13 @@
         <v>18</v>
       </c>
       <c r="H412" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1848</v>
+        <v>1.1791</v>
       </c>
       <c r="J412" t="n">
-        <v>21.3264</v>
+        <v>21.2238</v>
       </c>
     </row>
     <row r="413">
@@ -20706,13 +20706,13 @@
         <v>18</v>
       </c>
       <c r="H413" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I413" t="n">
-        <v>0.4456</v>
+        <v>0.4355</v>
       </c>
       <c r="J413" t="n">
-        <v>8.020799999999999</v>
+        <v>7.839</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.17</v>
       </c>
       <c r="I414" t="n">
-        <v>0.2526</v>
+        <v>0.2529</v>
       </c>
       <c r="J414" t="n">
-        <v>4.5468</v>
+        <v>4.5522</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.99</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.0495</v>
+        <v>-0.0492</v>
       </c>
       <c r="J415" t="n">
-        <v>-0.891</v>
+        <v>-0.8856000000000001</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.95</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.1113</v>
+        <v>-0.111</v>
       </c>
       <c r="J416" t="n">
-        <v>-2.0034</v>
+        <v>-1.998</v>
       </c>
     </row>
     <row r="417">
@@ -23669,10 +23669,10 @@
         <v>1.41</v>
       </c>
       <c r="I487" t="n">
-        <v>0.8196</v>
+        <v>0.8206</v>
       </c>
       <c r="J487" t="n">
-        <v>22.9488</v>
+        <v>22.9768</v>
       </c>
     </row>
     <row r="488">
@@ -23706,13 +23706,13 @@
         <v>28</v>
       </c>
       <c r="H488" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I488" t="n">
-        <v>-0.089</v>
+        <v>-0.1015</v>
       </c>
       <c r="J488" t="n">
-        <v>-2.492</v>
+        <v>-2.842</v>
       </c>
     </row>
     <row r="489">
@@ -23749,10 +23749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.23</v>
+        <v>-0.2298</v>
       </c>
       <c r="J489" t="n">
-        <v>-6.44</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="490">
@@ -23789,10 +23789,10 @@
         <v>0.68</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.3533</v>
+        <v>-0.3531</v>
       </c>
       <c r="J490" t="n">
-        <v>-9.8924</v>
+        <v>-9.886799999999999</v>
       </c>
     </row>
     <row r="491">
@@ -23829,10 +23829,10 @@
         <v>0.5</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.5122</v>
+        <v>-0.512</v>
       </c>
       <c r="J491" t="n">
-        <v>-14.3416</v>
+        <v>-14.336</v>
       </c>
     </row>
     <row r="492">
@@ -25869,10 +25869,10 @@
         <v>1.06</v>
       </c>
       <c r="I542" t="n">
-        <v>0.1948</v>
+        <v>0.1953</v>
       </c>
       <c r="J542" t="n">
-        <v>4.0908</v>
+        <v>4.1013</v>
       </c>
     </row>
     <row r="543">
@@ -25909,10 +25909,10 @@
         <v>1</v>
       </c>
       <c r="I543" t="n">
-        <v>0.0188</v>
+        <v>0.0193</v>
       </c>
       <c r="J543" t="n">
-        <v>0.3948</v>
+        <v>0.4053</v>
       </c>
     </row>
     <row r="544">
@@ -25946,13 +25946,13 @@
         <v>21</v>
       </c>
       <c r="H544" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I544" t="n">
-        <v>-0.1152</v>
+        <v>-0.1268</v>
       </c>
       <c r="J544" t="n">
-        <v>-2.4192</v>
+        <v>-2.6628</v>
       </c>
     </row>
     <row r="545">
@@ -25989,10 +25989,10 @@
         <v>0.87</v>
       </c>
       <c r="I545" t="n">
-        <v>-0.1703</v>
+        <v>-0.1701</v>
       </c>
       <c r="J545" t="n">
-        <v>-3.5763</v>
+        <v>-3.5721</v>
       </c>
     </row>
     <row r="546">
@@ -26029,10 +26029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I546" t="n">
-        <v>-0.4617</v>
+        <v>-0.4615</v>
       </c>
       <c r="J546" t="n">
-        <v>-9.6957</v>
+        <v>-9.6915</v>
       </c>
     </row>
     <row r="547">
@@ -26118,7 +26118,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -26158,7 +26158,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -29466,13 +29466,13 @@
         <v>20</v>
       </c>
       <c r="H632" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I632" t="n">
-        <v>0.9401</v>
+        <v>0.922</v>
       </c>
       <c r="J632" t="n">
-        <v>18.802</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="633">
@@ -29509,10 +29509,10 @@
         <v>1.37</v>
       </c>
       <c r="I633" t="n">
-        <v>0.8834</v>
+        <v>0.8838</v>
       </c>
       <c r="J633" t="n">
-        <v>17.668</v>
+        <v>17.676</v>
       </c>
     </row>
     <row r="634">
@@ -29549,10 +29549,10 @@
         <v>1.31</v>
       </c>
       <c r="I634" t="n">
-        <v>0.7659</v>
+        <v>0.7662</v>
       </c>
       <c r="J634" t="n">
-        <v>15.318</v>
+        <v>15.324</v>
       </c>
     </row>
     <row r="635">
@@ -29589,10 +29589,10 @@
         <v>1.1</v>
       </c>
       <c r="I635" t="n">
-        <v>0.3037</v>
+        <v>0.304</v>
       </c>
       <c r="J635" t="n">
-        <v>6.074</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="636">
@@ -29629,10 +29629,10 @@
         <v>1.02</v>
       </c>
       <c r="I636" t="n">
-        <v>0.0607</v>
+        <v>0.0611</v>
       </c>
       <c r="J636" t="n">
-        <v>1.214</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="637">
@@ -30469,10 +30469,10 @@
         <v>1.28</v>
       </c>
       <c r="I657" t="n">
-        <v>0.5863</v>
+        <v>0.587</v>
       </c>
       <c r="J657" t="n">
-        <v>11.726</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="658">
@@ -30509,10 +30509,10 @@
         <v>1.04</v>
       </c>
       <c r="I658" t="n">
-        <v>0.1362</v>
+        <v>0.1366</v>
       </c>
       <c r="J658" t="n">
-        <v>2.724</v>
+        <v>2.732</v>
       </c>
     </row>
     <row r="659">
@@ -30549,10 +30549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I659" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0946</v>
       </c>
       <c r="J659" t="n">
-        <v>-1.894</v>
+        <v>-1.892</v>
       </c>
     </row>
     <row r="660">
@@ -30589,10 +30589,10 @@
         <v>0.86</v>
       </c>
       <c r="I660" t="n">
-        <v>-0.1848</v>
+        <v>-0.1846</v>
       </c>
       <c r="J660" t="n">
-        <v>-3.696</v>
+        <v>-3.692</v>
       </c>
     </row>
     <row r="661">
@@ -30626,13 +30626,13 @@
         <v>20</v>
       </c>
       <c r="H661" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I661" t="n">
-        <v>-0.4835</v>
+        <v>-0.492</v>
       </c>
       <c r="J661" t="n">
-        <v>-9.67</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="662">
@@ -31469,10 +31469,10 @@
         <v>1.08</v>
       </c>
       <c r="I682" t="n">
-        <v>0.2292</v>
+        <v>0.2287</v>
       </c>
       <c r="J682" t="n">
-        <v>4.8132</v>
+        <v>4.8027</v>
       </c>
     </row>
     <row r="683">
@@ -31506,13 +31506,13 @@
         <v>21</v>
       </c>
       <c r="H683" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0113</v>
+        <v>0.0553</v>
       </c>
       <c r="J683" t="n">
-        <v>0.2373</v>
+        <v>1.1613</v>
       </c>
     </row>
     <row r="684">
@@ -31549,10 +31549,10 @@
         <v>0.91</v>
       </c>
       <c r="I684" t="n">
-        <v>-0.1291</v>
+        <v>-0.1292</v>
       </c>
       <c r="J684" t="n">
-        <v>-2.7111</v>
+        <v>-2.7132</v>
       </c>
     </row>
     <row r="685">
@@ -31589,10 +31589,10 @@
         <v>0.83</v>
       </c>
       <c r="I685" t="n">
-        <v>-0.2146</v>
+        <v>-0.2148</v>
       </c>
       <c r="J685" t="n">
-        <v>-4.5066</v>
+        <v>-4.5108</v>
       </c>
     </row>
     <row r="686">
@@ -31629,10 +31629,10 @@
         <v>0.77</v>
       </c>
       <c r="I686" t="n">
-        <v>-0.274</v>
+        <v>-0.2742</v>
       </c>
       <c r="J686" t="n">
-        <v>-5.754</v>
+        <v>-5.7582</v>
       </c>
     </row>
     <row r="687">
@@ -32386,13 +32386,13 @@
         <v>30</v>
       </c>
       <c r="H705" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I705" t="n">
-        <v>-0.0461</v>
+        <v>-0.0284</v>
       </c>
       <c r="J705" t="n">
-        <v>-1.383</v>
+        <v>-0.852</v>
       </c>
     </row>
     <row r="706">
@@ -32426,13 +32426,13 @@
         <v>30</v>
       </c>
       <c r="H706" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I706" t="n">
-        <v>-0.1951</v>
+        <v>-0.2057</v>
       </c>
       <c r="J706" t="n">
-        <v>-5.853</v>
+        <v>-6.171</v>
       </c>
     </row>
     <row r="707">
@@ -35438,7 +35438,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -35466,19 +35466,19 @@
         <v>19</v>
       </c>
       <c r="H782" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I782" t="n">
-        <v>1.4075</v>
+        <v>1.3955</v>
       </c>
       <c r="J782" t="n">
-        <v>26.7425</v>
+        <v>26.5145</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -35509,10 +35509,10 @@
         <v>1.75</v>
       </c>
       <c r="I783" t="n">
-        <v>1.3951</v>
+        <v>1.3955</v>
       </c>
       <c r="J783" t="n">
-        <v>26.5069</v>
+        <v>26.5145</v>
       </c>
     </row>
     <row r="784">
@@ -35549,10 +35549,10 @@
         <v>1.29</v>
       </c>
       <c r="I784" t="n">
-        <v>0.7116</v>
+        <v>0.7119</v>
       </c>
       <c r="J784" t="n">
-        <v>13.5204</v>
+        <v>13.5261</v>
       </c>
     </row>
     <row r="785">
@@ -35589,10 +35589,10 @@
         <v>1.06</v>
       </c>
       <c r="I785" t="n">
-        <v>0.1722</v>
+        <v>0.1725</v>
       </c>
       <c r="J785" t="n">
-        <v>3.2718</v>
+        <v>3.2775</v>
       </c>
     </row>
     <row r="786">
@@ -35629,10 +35629,10 @@
         <v>0.98</v>
       </c>
       <c r="I786" t="n">
-        <v>-0.1625</v>
+        <v>-0.1622</v>
       </c>
       <c r="J786" t="n">
-        <v>-3.0875</v>
+        <v>-3.0818</v>
       </c>
     </row>
     <row r="787">
@@ -37069,10 +37069,10 @@
         <v>1.27</v>
       </c>
       <c r="I822" t="n">
-        <v>0.5911</v>
+        <v>0.5903</v>
       </c>
       <c r="J822" t="n">
-        <v>12.4131</v>
+        <v>12.3963</v>
       </c>
     </row>
     <row r="823">
@@ -37109,10 +37109,10 @@
         <v>0.84</v>
       </c>
       <c r="I823" t="n">
-        <v>-0.2005</v>
+        <v>-0.2007</v>
       </c>
       <c r="J823" t="n">
-        <v>-4.2105</v>
+        <v>-4.2147</v>
       </c>
     </row>
     <row r="824">
@@ -37146,13 +37146,13 @@
         <v>21</v>
       </c>
       <c r="H824" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I824" t="n">
-        <v>-0.2502</v>
+        <v>-0.2406</v>
       </c>
       <c r="J824" t="n">
-        <v>-5.2542</v>
+        <v>-5.0526</v>
       </c>
     </row>
     <row r="825">
@@ -37189,10 +37189,10 @@
         <v>0.75</v>
       </c>
       <c r="I825" t="n">
-        <v>-0.2887</v>
+        <v>-0.2889</v>
       </c>
       <c r="J825" t="n">
-        <v>-6.0627</v>
+        <v>-6.0669</v>
       </c>
     </row>
     <row r="826">
@@ -37229,10 +37229,10 @@
         <v>0.72</v>
       </c>
       <c r="I826" t="n">
-        <v>-0.317</v>
+        <v>-0.3172</v>
       </c>
       <c r="J826" t="n">
-        <v>-6.657</v>
+        <v>-6.6612</v>
       </c>
     </row>
     <row r="827">
@@ -38869,10 +38869,10 @@
         <v>1.47</v>
       </c>
       <c r="I867" t="n">
-        <v>1.0287</v>
+        <v>1.0292</v>
       </c>
       <c r="J867" t="n">
-        <v>17.4879</v>
+        <v>17.4964</v>
       </c>
     </row>
     <row r="868">
@@ -38906,13 +38906,13 @@
         <v>17</v>
       </c>
       <c r="H868" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I868" t="n">
-        <v>0.983</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J868" t="n">
-        <v>16.711</v>
+        <v>16.4424</v>
       </c>
     </row>
     <row r="869">
@@ -38949,10 +38949,10 @@
         <v>1.4</v>
       </c>
       <c r="I869" t="n">
-        <v>0.916</v>
+        <v>0.9163</v>
       </c>
       <c r="J869" t="n">
-        <v>15.572</v>
+        <v>15.5771</v>
       </c>
     </row>
     <row r="870">
@@ -38986,13 +38986,13 @@
         <v>17</v>
       </c>
       <c r="H870" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I870" t="n">
-        <v>0.916</v>
+        <v>0.8985</v>
       </c>
       <c r="J870" t="n">
-        <v>15.572</v>
+        <v>15.2745</v>
       </c>
     </row>
     <row r="871">
@@ -39029,10 +39029,10 @@
         <v>1.33</v>
       </c>
       <c r="I871" t="n">
-        <v>0.7852</v>
+        <v>0.7857</v>
       </c>
       <c r="J871" t="n">
-        <v>13.3484</v>
+        <v>13.3569</v>
       </c>
     </row>
     <row r="872">
@@ -39066,13 +39066,13 @@
         <v>23</v>
       </c>
       <c r="H872" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I872" t="n">
-        <v>0.763</v>
+        <v>0.7772</v>
       </c>
       <c r="J872" t="n">
-        <v>17.549</v>
+        <v>17.8756</v>
       </c>
     </row>
     <row r="873">
@@ -39109,10 +39109,10 @@
         <v>1.41</v>
       </c>
       <c r="I873" t="n">
-        <v>0.763</v>
+        <v>0.7623</v>
       </c>
       <c r="J873" t="n">
-        <v>17.549</v>
+        <v>17.5329</v>
       </c>
     </row>
     <row r="874">
@@ -39149,10 +39149,10 @@
         <v>0.89</v>
       </c>
       <c r="I874" t="n">
-        <v>-0.1591</v>
+        <v>-0.1593</v>
       </c>
       <c r="J874" t="n">
-        <v>-3.6593</v>
+        <v>-3.6639</v>
       </c>
     </row>
     <row r="875">
@@ -39189,10 +39189,10 @@
         <v>0.86</v>
       </c>
       <c r="I875" t="n">
-        <v>-0.1918</v>
+        <v>-0.192</v>
       </c>
       <c r="J875" t="n">
-        <v>-4.4114</v>
+        <v>-4.416</v>
       </c>
     </row>
     <row r="876">
@@ -39229,10 +39229,10 @@
         <v>0.48</v>
       </c>
       <c r="I876" t="n">
-        <v>-0.5404</v>
+        <v>-0.5405</v>
       </c>
       <c r="J876" t="n">
-        <v>-12.4292</v>
+        <v>-12.4315</v>
       </c>
     </row>
     <row r="877">
@@ -39266,13 +39266,13 @@
         <v>23</v>
       </c>
       <c r="H877" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I877" t="n">
-        <v>1.0142</v>
+        <v>0.9979</v>
       </c>
       <c r="J877" t="n">
-        <v>23.3266</v>
+        <v>22.9517</v>
       </c>
     </row>
     <row r="878">
@@ -39309,10 +39309,10 @@
         <v>1.35</v>
       </c>
       <c r="I878" t="n">
-        <v>0.8833</v>
+        <v>0.884</v>
       </c>
       <c r="J878" t="n">
-        <v>20.3159</v>
+        <v>20.332</v>
       </c>
     </row>
     <row r="879">
@@ -39349,10 +39349,10 @@
         <v>1.02</v>
       </c>
       <c r="I879" t="n">
-        <v>0.0876</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J879" t="n">
-        <v>2.0148</v>
+        <v>2.0217</v>
       </c>
     </row>
     <row r="880">
@@ -39389,10 +39389,10 @@
         <v>0.85</v>
       </c>
       <c r="I880" t="n">
-        <v>-0.4863</v>
+        <v>-0.4859</v>
       </c>
       <c r="J880" t="n">
-        <v>-11.1849</v>
+        <v>-11.1757</v>
       </c>
     </row>
     <row r="881">
@@ -39429,10 +39429,10 @@
         <v>0.79</v>
       </c>
       <c r="I881" t="n">
-        <v>-0.6278</v>
+        <v>-0.6274</v>
       </c>
       <c r="J881" t="n">
-        <v>-14.4394</v>
+        <v>-14.4302</v>
       </c>
     </row>
     <row r="882">
@@ -40466,13 +40466,13 @@
         <v>21</v>
       </c>
       <c r="H907" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I907" t="n">
-        <v>0.8419</v>
+        <v>0.8277</v>
       </c>
       <c r="J907" t="n">
-        <v>17.6799</v>
+        <v>17.3817</v>
       </c>
     </row>
     <row r="908">
@@ -40509,10 +40509,10 @@
         <v>0.98</v>
       </c>
       <c r="I908" t="n">
-        <v>-0.0404</v>
+        <v>-0.0402</v>
       </c>
       <c r="J908" t="n">
-        <v>-0.8484</v>
+        <v>-0.8442</v>
       </c>
     </row>
     <row r="909">
@@ -40549,10 +40549,10 @@
         <v>0.83</v>
       </c>
       <c r="I909" t="n">
-        <v>-0.2182</v>
+        <v>-0.218</v>
       </c>
       <c r="J909" t="n">
-        <v>-4.5822</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="910">
@@ -40589,10 +40589,10 @@
         <v>0.76</v>
       </c>
       <c r="I910" t="n">
-        <v>-0.2873</v>
+        <v>-0.2871</v>
       </c>
       <c r="J910" t="n">
-        <v>-6.0333</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="911">
@@ -40629,10 +40629,10 @@
         <v>0.76</v>
       </c>
       <c r="I911" t="n">
-        <v>-0.2873</v>
+        <v>-0.2871</v>
       </c>
       <c r="J911" t="n">
-        <v>-6.0333</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="912">
@@ -42066,13 +42066,13 @@
         <v>23</v>
       </c>
       <c r="H947" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I947" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6757</v>
       </c>
       <c r="J947" t="n">
-        <v>15.0581</v>
+        <v>15.5411</v>
       </c>
     </row>
     <row r="948">
@@ -42186,13 +42186,13 @@
         <v>23</v>
       </c>
       <c r="H950" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I950" t="n">
-        <v>0.3896</v>
+        <v>0.3651</v>
       </c>
       <c r="J950" t="n">
-        <v>8.960800000000001</v>
+        <v>8.3973</v>
       </c>
     </row>
     <row r="951">
